--- a/2022 data/excel_outputs/323_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/323_boothwise_data.xlsx
@@ -14,1260 +14,1452 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="507">
   <si>
     <t>AC 323 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
+    <t>Unnamed: 27</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>##### #### ##0##0##### #0#0 1</t>
-  </si>
-  <si>
-    <t>##### #### ##0##0##### #0#0 2</t>
-  </si>
-  <si>
-    <t>#### #### ##0##0##0 ######### #### ######### ##### #0##1</t>
-  </si>
-  <si>
-    <t>#### #### ##0#0##0 ######### #### ######### ##### #0#02#####</t>
-  </si>
-  <si>
-    <t>#### #### ##0#0##0 ######### #### ######### ##### #0#03#####</t>
-  </si>
-  <si>
-    <t>#### #### ##0#0##0 ######### #### ######### ##### #0#04#####</t>
-  </si>
-  <si>
-    <t>##0##0 ######### ###### ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>##0##0 ######### ###### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>##0##0 ######### ###### ####### #0##0 3</t>
-  </si>
-  <si>
-    <t>##0##0 ######### ###### ####### #0##0 4</t>
-  </si>
-  <si>
-    <t>##0##0 ######### ###### ####### #0##0 5</t>
-  </si>
-  <si>
-    <t>##0##0 ######### ###### ####### #0##0 6</t>
-  </si>
-  <si>
-    <t>##0##0 ######### ###### ####### #0##0 7</t>
-  </si>
-  <si>
-    <t>##0##0 ######### ###### ####### #0##0 8</t>
-  </si>
-  <si>
-    <t>#### ###### ##0##0###### ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>#### ###### ##0##0###### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>#### ###### ##0##0###### ####### #0##0 3</t>
-  </si>
-  <si>
-    <t>#### ###### ##0##0###### ####### #0##0 4</t>
-  </si>
-  <si>
-    <t>##### #### ##### ####### ####### ### #0#0 1</t>
-  </si>
-  <si>
-    <t>##### #### ##### ####### ####### ### #0#0 2</t>
-  </si>
-  <si>
-    <t>##### #### ##### ####### ####### ### #0#0 3</t>
-  </si>
-  <si>
-    <t>##### #### ##### ####### ####### ### #0#0 4</t>
-  </si>
-  <si>
-    <t>##### #### ##### ####### ####### ### #0#0 5</t>
-  </si>
-  <si>
-    <t>##### #### ##### ####### ###### ### #0#0 1</t>
-  </si>
-  <si>
-    <t>##### #### ##### ####### ###### ### #0#0 2</t>
-  </si>
-  <si>
-    <t>##### #### ##### ####### ###### ### #0#0 3</t>
-  </si>
-  <si>
-    <t>##### #### ##### ####### ###### ### #0#0 4</t>
-  </si>
-  <si>
-    <t>####### ###### ##0 ########## ######### #0##0 1</t>
-  </si>
-  <si>
-    <t>####### ###### ##0 ########## ######### #0##0 2</t>
-  </si>
-  <si>
-    <t>####### ###### ##0 ########## ######### #0##0 3</t>
-  </si>
-  <si>
-    <t>####### ###### ##0 ########## ######### #0##0 4</t>
-  </si>
-  <si>
-    <t>####### ###### ##0 ########## ######### #0##0 5</t>
-  </si>
-  <si>
-    <t>####### ###### ##0 ########## ######### #0##0 6</t>
-  </si>
-  <si>
-    <t>####### ###### ##0 ########## ######### #0##0 7</t>
-  </si>
-  <si>
-    <t>##0##0 ######### ###### ####### #0 ##0 1</t>
-  </si>
-  <si>
-    <t>##0##0 ######### ###### ####### #0 ##0 2</t>
-  </si>
-  <si>
-    <t>##0##0 ######### ###### ####### #0 ##0 3</t>
-  </si>
-  <si>
-    <t>##0##0 ######### ###### ####### #0 ##0 4</t>
-  </si>
-  <si>
-    <t>##0##0 ######### ###### ####### #0 ##0 5</t>
-  </si>
-  <si>
-    <t>##0##0 ######### ###### ####### #0 ##0 6</t>
-  </si>
-  <si>
-    <t>###### #### ###### ##0##0 ######### ####### #0##0 #</t>
-  </si>
-  <si>
-    <t>###### ###### #### ##0##0##### ######### ###### #0### 1</t>
-  </si>
-  <si>
-    <t>###### ###### #### ##0##0##### ######### ###### #0### 2</t>
-  </si>
-  <si>
-    <t>###### ###### #### ##0##0##### ######### ###### #0### 3</t>
-  </si>
-  <si>
-    <t>###### ###### #### ##0##0##### ######### ###### #0### 4</t>
-  </si>
-  <si>
-    <t>##0##0##0##0##0 ############ ######### #0### 1</t>
-  </si>
-  <si>
-    <t>##0##0##0##0##0 ############ ######### #0### 2</t>
-  </si>
-  <si>
-    <t>##0##0##0##0##0 ############ ######### #0### 3</t>
-  </si>
-  <si>
-    <t>##0##0##0##0##0 ############ ######### #0### 4</t>
-  </si>
-  <si>
-    <t>#0##0#0 ######## ######### #0### 1</t>
-  </si>
-  <si>
-    <t>#0##0#0 ######## ######### #0### 2</t>
-  </si>
-  <si>
-    <t>##0##0###### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>##0##0###### ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>##0##0###### ###### #0##0 3</t>
-  </si>
-  <si>
-    <t>##0##0###### ###### #0##0 4</t>
-  </si>
-  <si>
-    <t>##0##0###### ###### #0##0 5</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ##### ##### #0### 1</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ##### ##### #0### 2</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ##### ##### #0### 3</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ##### ##### #0### 4</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ##### ##### #0### 5</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ##### ##### #0### 6</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ##### ##### #0### 7</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ##### ##### #0### 8</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ##### ##### #0### 9</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ##### ##### #0### 10</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ##### ##### #0### 11</t>
-  </si>
-  <si>
-    <t>####### ###### ##### ##### ##### ######### #0##0 1</t>
-  </si>
-  <si>
-    <t>####### ###### ##### ##### ##### ######### #0##0 2</t>
-  </si>
-  <si>
-    <t>####### ###### ##### ##### ##### ######### #0##0 3</t>
-  </si>
-  <si>
-    <t>####### ###### ##### ##### ##### ######### #0##0 4</t>
-  </si>
-  <si>
-    <t>####### ###### ##### ########### ######### #0### 1</t>
-  </si>
-  <si>
-    <t>####### ###### ##### ########### ######### #0### 2</t>
-  </si>
-  <si>
-    <t>####### ###### ##### ########### ######### #0### 3</t>
-  </si>
-  <si>
-    <t>####### ###### ##### ########### ######### #0### 4</t>
-  </si>
-  <si>
-    <t>####### ###### ##### ########### ######### #0### 5</t>
-  </si>
-  <si>
-    <t>####### ###### ##### ########### ######### #0### 6</t>
-  </si>
-  <si>
-    <t>####### ###### ##### ########### ######### #0### 7</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #0##0 3</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #0##0 4</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #0##0 5</t>
-  </si>
-  <si>
-    <t>###nn #0 ######### ###### ######### #0##0 1</t>
-  </si>
-  <si>
-    <t>###nn #0 ######### ###### ######### #0##0 2</t>
-  </si>
-  <si>
-    <t>###nn #0 ######### ###### ######### #0##0 3</t>
-  </si>
-  <si>
-    <t>###nn #0 ######### ###### ######### #0##0 4</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######### ##### ######## #0### 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######### ##### ######## #0### 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######### ##### ######## #0### 3</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######### ##### ######## #0### 4</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######### ##### ######## #0### 5</t>
-  </si>
-  <si>
-    <t>######## ##### ##0##0 ##### ####### ######## #0### 1</t>
-  </si>
-  <si>
-    <t>######## ##### ##0##0 ##### ####### ######## #0### 2</t>
-  </si>
-  <si>
-    <t>######## ##### ##0##0 ##### ####### ######## #0### 3</t>
-  </si>
-  <si>
-    <t>######## ##### ##0##0 ##### ####### ######## #0### 4</t>
-  </si>
-  <si>
-    <t>######## ##### ##0##0 ##### ####### ######## #0### 5</t>
-  </si>
-  <si>
-    <t>######## ##### ##0##0 ##### ####### ######## #0### 6</t>
-  </si>
-  <si>
-    <t>######## ##### ##0##0 ##### ####### ######## #0### 7</t>
-  </si>
-  <si>
-    <t>######## ##### ##0##0 ##### ####### ######## #0### 8</t>
-  </si>
-  <si>
-    <t>######### ###### ##### ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>######### ###### ##### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>######### ###### ##### ####### #0##0 3</t>
-  </si>
-  <si>
-    <t>######### ###### ##### ####### #0##0 4</t>
-  </si>
-  <si>
-    <t>######### ###### ##### ####### #0##0 5</t>
-  </si>
-  <si>
-    <t>######### ###### ##### ####### #0##0 6</t>
-  </si>
-  <si>
-    <t>######### ###### ##### ####### #0##0 7</t>
-  </si>
-  <si>
-    <t>##### ##0 ##0 ########## ######## #0##0 1</t>
-  </si>
-  <si>
-    <t>##### ##0 ##0 ########## ######## #0##0 2</t>
-  </si>
-  <si>
-    <t>##### ##0 ##0 ########## ######## #0##0 3</t>
-  </si>
-  <si>
-    <t>##### ##0 ##0 ########## ######## #0##0 4</t>
-  </si>
-  <si>
-    <t>##### ##0 ##0 ########## ######## #0##0 5</t>
-  </si>
-  <si>
-    <t>##### ##0 ##0 ########## ######## #0##0 6</t>
-  </si>
-  <si>
-    <t>##### ##0 ##0 ########## ######## #0##0 7</t>
-  </si>
-  <si>
-    <t>##### ##0 ##0 ########## ######## #0##0 8</t>
-  </si>
-  <si>
-    <t>##### ##0 ##0 ########## ######## #0##0 9</t>
-  </si>
-  <si>
-    <t>##### ##0 ##0 ########## ######## #0##0 10</t>
-  </si>
-  <si>
-    <t>##### ##0 ##0 ########## ######## #0##0 11</t>
-  </si>
-  <si>
-    <t>##### ##0 ##0 ########## ######## #0##0 12</t>
-  </si>
-  <si>
-    <t>##### ##0 ##0 ########## ######## #0##0 13</t>
-  </si>
-  <si>
-    <t>###### ##### ##0##0 ##### ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>###### ##### ##0##0 ##### ##### #0##0 2</t>
-  </si>
-  <si>
-    <t>###### ##### ##0##0 ##### ##### #0##0 3</t>
-  </si>
-  <si>
-    <t>###### ##### ##0##0 ##### ##### #0##0 4</t>
-  </si>
-  <si>
-    <t>###### ##### ##0##0 ##### ##### #0##0 5</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ######## #0##0 1 #########</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ######## #0##0 2 #########</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ######## #0##0 3 #########</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ######## #0##0 4 #########</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ######## #0##0 5 #########</t>
-  </si>
-  <si>
-    <t>###### ######### ##### ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>###### ######### ##### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>###### ######### ##### ####### #0##0 3</t>
-  </si>
-  <si>
-    <t>###### ######### ##### ####### #0##0 4</t>
-  </si>
-  <si>
-    <t>###### ######### ##### ####### #0##0 5</t>
-  </si>
-  <si>
-    <t>###### ######### ##### ####### #0##0 6</t>
-  </si>
-  <si>
-    <t>###### ###### #0##0 ######## ### #0##0 10</t>
-  </si>
-  <si>
-    <t>###### ###### #0##0 ######## ### #0##0 11</t>
-  </si>
-  <si>
-    <t>###### ###### #0##0 ######## ### #0##0 12</t>
-  </si>
-  <si>
-    <t>####0##0###### ##### ###### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0###### ##### ###### ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0###### ##### ###### ###### #0##0 3</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####### #0### 1</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####### #0### 2</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####### #0### 3</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####### #0### 4</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####### #0### 5</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####### #0### 6</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####### #0### 7</t>
-  </si>
-  <si>
-    <t>####0##0########### ########### #0### 1</t>
-  </si>
-  <si>
-    <t>####0##0########### ########### #0##02</t>
-  </si>
-  <si>
-    <t>##0##0##0########### ########### #0##0 1</t>
-  </si>
-  <si>
-    <t>##0##0##0########### ########### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##### ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##### ##### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##### ##### #0##0 3</t>
-  </si>
-  <si>
-    <t>####### ####### ########### #0### 1</t>
-  </si>
-  <si>
-    <t>####### ####### ########### #0### 2</t>
-  </si>
-  <si>
-    <t>####### ####### ########### #0### 3</t>
-  </si>
-  <si>
-    <t>######## ##0##0 ####### ##0 ##0 8</t>
-  </si>
-  <si>
-    <t>######## ##0##0 ####### ##0 ##0 9</t>
-  </si>
-  <si>
-    <t>######## ##0##0 ####### ##0 ##0 10</t>
-  </si>
-  <si>
-    <t>######## ###### ##### ######## #0##0 1</t>
-  </si>
-  <si>
-    <t>######## ###### ##### ######## #0##0 2</t>
-  </si>
-  <si>
-    <t>######## ###### ##### ######## #0##0 3</t>
-  </si>
-  <si>
-    <t>######## ###### ##### ######## #0##0 4</t>
-  </si>
-  <si>
-    <t>######## ###### ##### ######## #0##0 5</t>
-  </si>
-  <si>
-    <t>######### ##### ######### #0### 1</t>
-  </si>
-  <si>
-    <t>######### ##### ######### #0### 2</t>
-  </si>
-  <si>
-    <t>######### ##### ######### #0### 3</t>
-  </si>
-  <si>
-    <t>######### ##### ######### #0### 4</t>
-  </si>
-  <si>
-    <t>######### ##### ######### #0### 5</t>
-  </si>
-  <si>
-    <t>######### ##### ######### #0### 6</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ######### ##0 #0### 1</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ######### ##0 #0### 2</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ######### ##0 #0### 3</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ######### ##0 #0### 4</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ######### ##0 #0### 5</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ######### ##0 #0### 6</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ######### ##0 #0### 7</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ######### ##0 #0### 8</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ######### ##0 #0### 9</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ######### ##0 #0### 10</t>
-  </si>
-  <si>
-    <t>####0##0#### ###### ## #### #0### 1</t>
-  </si>
-  <si>
-    <t>####0##0#### ###### ## #### #0### 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### ###### ######## #0### 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### ###### ######## #0### 2</t>
-  </si>
-  <si>
-    <t>#### ###### ##0##0######## #0### 1</t>
-  </si>
-  <si>
-    <t>#### ###### ##0##0######## #0### 2</t>
-  </si>
-  <si>
-    <t>#### ###### ##0##0######## #0### 3</t>
-  </si>
-  <si>
-    <t>#### ###### ##0##0######## #0### 4</t>
-  </si>
-  <si>
-    <t>#### ###### ##0##0######## #0### 5</t>
-  </si>
-  <si>
-    <t>#### ###### ##0##0######## #0### 6</t>
-  </si>
-  <si>
-    <t>#### ###### ##0##0######## #0### 7</t>
-  </si>
-  <si>
-    <t>#### ###### ##0##0######## #0### 8</t>
-  </si>
-  <si>
-    <t>#### ###### ##0##0######## #0### 9</t>
-  </si>
-  <si>
-    <t>#### ###### ##0##0######## #0### 10</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######## #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>##### #### ##### ##### #### #0##0 1</t>
-  </si>
-  <si>
-    <t>##### #### ##### ##### #### #0##0 2</t>
-  </si>
-  <si>
-    <t>##### #### ##### ##### #### #0##0 3</t>
-  </si>
-  <si>
-    <t>##### #### ##### ##### #### #0##0 4</t>
-  </si>
-  <si>
-    <t>##### #### ##### ##### #### #0##0 5</t>
-  </si>
-  <si>
-    <t>##### #### ##### ##### #### #0##0 6</t>
-  </si>
-  <si>
-    <t>##### #### ##### ##### #### #0##0 7</t>
-  </si>
-  <si>
-    <t>##### #### ##### ##### #### #0##0 8</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ##### #0### 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ##### #0### 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### #0 ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### #0 ##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ##0 #0### 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### #0### 1</t>
-  </si>
-  <si>
-    <t>##0##0##### ##### #0### 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #0### 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #0### 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>######### #### #0##0 1</t>
-  </si>
-  <si>
-    <t>######### #### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #### ### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #### ### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #### ### #0##0 3</t>
-  </si>
-  <si>
-    <t>######### ######## #0### 1</t>
-  </si>
-  <si>
-    <t>##0 ########### ########## ######## #0### 1</t>
-  </si>
-  <si>
-    <t>######### ######## #0### 2</t>
-  </si>
-  <si>
-    <t>######### ######## #0### 3</t>
-  </si>
-  <si>
-    <t>####0 ##0 ########;######ddh #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #0### 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #0### 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #0### 3</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #0 ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #0 ##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #0 ##0 3</t>
-  </si>
-  <si>
-    <t>######### ##### ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>######### ##### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######## #### ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #0 ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #0 ##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### #0### 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### #0### 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### #0### 3</t>
-  </si>
-  <si>
-    <t>####0 ##0 ########## #0### 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ########## #0### 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ########## #0### 3</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ########## #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##0 ########## #0### 1</t>
-  </si>
-  <si>
-    <t>#### ##### #### ##0##0 ##0 #### ##### ###### #0### 1</t>
-  </si>
-  <si>
-    <t>#### ##### #### ##0##0 ##0 #### ##### ###### #0### 2</t>
-  </si>
-  <si>
-    <t>#### ##### #### ##0##0 ##0 #### ##### ###### #0### 3</t>
-  </si>
-  <si>
-    <t>#### ##### #### ##0##0 ##0 #### ##### ###### #0### 4</t>
-  </si>
-  <si>
-    <t>#### ##### #### ##0##0 ##0 #### ##### ###### #0### 5</t>
-  </si>
-  <si>
-    <t>#### ##### #### ##0##0 ##0 #### ##### ###### #0### 6</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ##0 #### ##### ###### #0 ##0 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ##0 #### ##### ###### #0#0 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ##0 #### ##### ###### #0#0 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ##0 #### ##### ###### #0### 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ##0 #### ##### ###### #0 ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ##0 #### ##### ###### #0 ##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######## ##0 #### ##### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>#0#0 ##### #### ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>#0#0 ##### #### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### #### ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### #### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### #### ####### #0##0 3</t>
-  </si>
-  <si>
-    <t>#0#0 ##### #### ####### #0##0 3</t>
-  </si>
-  <si>
-    <t>####0 ##0 ### #### #0 ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ### #### ###### #0####</t>
-  </si>
-  <si>
-    <t>####0 ##0 ### #### ####### #0### 2</t>
-  </si>
-  <si>
-    <t>######## ##### #### ##### ####### ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>######## ##### #### ##### ####### ##### #0##0 2</t>
-  </si>
-  <si>
-    <t>######## ##### #### ##### ####### ##### #0##0 3</t>
-  </si>
-  <si>
-    <t>######## ##### #### ##### ####### ##### #0##0 4</t>
-  </si>
-  <si>
-    <t>######## #### ####### ##### ##### #0### 1</t>
-  </si>
-  <si>
-    <t>######## #### ####### ##### ##### #0### 2</t>
-  </si>
-  <si>
-    <t>######## #### ####### ##### ##### #0### 3</t>
-  </si>
-  <si>
-    <t>###### ### ######## #0### 1</t>
-  </si>
-  <si>
-    <t>###### ### ######## #0### 2</t>
-  </si>
-  <si>
-    <t>###### ### ######## #0### 3</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ###### #0### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ###### #0### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ###### #0### 3</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### #0##0 3</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### #0##0 4</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### #0##0 5</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### #0##0 6</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ######## #0##0 1</t>
-  </si>
-  <si>
-    <t>########## ####### #### ######## ########### #0### 1</t>
-  </si>
-  <si>
-    <t>########## ####### #### ######## ########### #0### 2</t>
-  </si>
-  <si>
-    <t>########## ####### #### ######## ########### #0### 3</t>
-  </si>
-  <si>
-    <t>##### ##### ###### ######## ########### #0##0 1</t>
-  </si>
-  <si>
-    <t>##### ##### ###### ######## ########### #0##0 2</t>
-  </si>
-  <si>
-    <t>##### ##### ###### ######## ########### #0##0 3</t>
-  </si>
-  <si>
-    <t>##### ##### ###### ######## ########### #0##0 4</t>
-  </si>
-  <si>
-    <t>########## ####### #### ######## ########### #0### 4</t>
-  </si>
-  <si>
-    <t>########## ####### #### ######## ########### #0###5</t>
-  </si>
-  <si>
-    <t>########## ####### #### ######## ########### #0### 6</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ####### #0### 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ####### #0### 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ####### #0### 3</t>
-  </si>
-  <si>
-    <t>######### ####### ####### #0### 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 #### #0##0 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 #### #0##0 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 #### #0##0 3</t>
-  </si>
-  <si>
-    <t>####### ###### ##### ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>####### ###### ##### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ##### #0 ### 1</t>
-  </si>
-  <si>
-    <t>### ###### ####### #### ;###### ddh ######## ####### #0 ### 1</t>
-  </si>
-  <si>
-    <t>### ###### ####### #### ;###### ddh ######## ####### #0 ### 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##0 ##### #### #### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##0 ##### #### #### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##0 ##### #### #### #0##0 3</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##0 ##### #### #### #0##0 4</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ##0 ##### #### #### #0### 1</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ##0 ##### #### #### #0### 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ### ######### ##3 #### 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #### ######### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #### ######### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #### ######### #0##0 3</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##0 ####### #### ######### #0### 1</t>
-  </si>
-  <si>
-    <t>######### ####### #### ######### #0### 1</t>
-  </si>
-  <si>
-    <t>######### ####### #### ######### #0### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0### 3</t>
-  </si>
-  <si>
-    <t>####### ##0##0 ##0 ##### #### ####### #0### 1</t>
-  </si>
-  <si>
-    <t>####### ##0##0 ##0 ##### #### ####### #0### 2</t>
-  </si>
-  <si>
-    <t>####### ##0##0 ##0 ##### #### ####### #0### 3</t>
-  </si>
-  <si>
-    <t>####### ##0##0 ##0 ##### #### ####### #0### 4</t>
-  </si>
-  <si>
-    <t>####### ##0##0 ##0 ##### #### ####### #0### 5</t>
-  </si>
-  <si>
-    <t>####### ##0##0 ##0 ##### #### ####### #0### 6</t>
-  </si>
-  <si>
-    <t>####0 ##0 ### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##0 ############# ##0 ##0 1</t>
-  </si>
-  <si>
-    <t>##0##0##0##0 ####### ###### #0### 1</t>
-  </si>
-  <si>
-    <t>##0##0##0##0 ####### ###### #0### 2</t>
-  </si>
-  <si>
-    <t>##0##0##### #### #0### 1</t>
-  </si>
-  <si>
-    <t>##0##0##### #### #0### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ######### #0### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #0### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #0### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #0### 3</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0#### #0### 1</t>
-  </si>
-  <si>
-    <t>####0##0#### #0### 2</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ###### #### #0##0 1</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ###### #### #0##0 2</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ###### #### #0##0 3</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ###### #### #0##0 4</t>
-  </si>
-  <si>
-    <t>######### ###### #0### 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######## ### #0### 1</t>
-  </si>
-  <si>
-    <t>######### #### #0####</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##### #0### 1</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ##0 ##### #### #####0### 1</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ##0 ##### #### #####0### 2</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ##0 ##### #### #####0### 3</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ##0 ##### #### #####0### 4</t>
-  </si>
-  <si>
-    <t>####0##0 ##0 ##### #### ##### #0### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##0 ##### #### ##### #0### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0##0 3</t>
-  </si>
-  <si>
-    <t>##0##0##0###### #0### 1</t>
-  </si>
-  <si>
-    <t>##0##0##0###### #0### 2</t>
-  </si>
-  <si>
-    <t>##### #0##0 ##0 ###### ##### #0### 1</t>
-  </si>
-  <si>
-    <t>##### #0##0 ##0 ###### ##### #0### 2</t>
-  </si>
-  <si>
-    <t>##### #0##0 ##0 ###### ##### #0### 3</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##0 ######## #### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##0 ######## ####### #0### 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##0 ####### #### #0### 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##0 ####### ####### #0### 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##0 ####### ##### #0### 3</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### #0##0 3</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### #0##0 4</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ########### #0 ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ########### #0 ##0 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### ####### ## ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### ####### ## ##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### ####### ## ##0 3</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### ####### ## ##0 4</t>
-  </si>
-  <si>
-    <t>###### ##### ##0 ### ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>###### ##### ##0 ### ##### #0##0 2</t>
-  </si>
-  <si>
-    <t>###### ##### ##0 ### ##### #0##0 3</t>
-  </si>
-  <si>
-    <t>###### ##### ##0 ### ##### #0##0 4</t>
-  </si>
-  <si>
-    <t>##### ####0 ##0 ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>##### ####0 ##0 ##### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### #0### 2</t>
-  </si>
-  <si>
-    <t>## ###### ### ####0##0 ##### #0## 3</t>
-  </si>
-  <si>
-    <t>## ###### ### ####0##0 ##### #0## 4</t>
-  </si>
-  <si>
-    <t>######### #### ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>######### #### ##### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##### ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>###### ### ##### #0 ##0 1</t>
-  </si>
-  <si>
-    <t>###### ### ##### #0 ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 #### ####### #0### 1</t>
-  </si>
-  <si>
-    <t>####0##0 #### ####### #0### 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ### #0##0 2</t>
-  </si>
-  <si>
-    <t>##0##0##### ##### ##### ### #### #0##0 1</t>
-  </si>
-  <si>
-    <t>##0##0##### ##### ##### ### #### #0##0 2</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ### #0##0 1</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ### #0##0 2</t>
+    <t>SE T JOSAPH IM0KA0P N K0N0 1</t>
+  </si>
+  <si>
+    <t>SE T JOSAPH IM0KA0 P N K0N02</t>
+  </si>
+  <si>
+    <t>SE T JOSAPH I0KA0 P N K0N03</t>
+  </si>
+  <si>
+    <t>SE T JOSAPH IM0KA0P N K0N04</t>
+  </si>
+  <si>
+    <t>MAINA DE VI BA0IM0KA0 MAJAPUR UPH BAL DAPUR</t>
+  </si>
+  <si>
+    <t>KH TA K0N01 MAINA DE VI BA0I0KA0 MAJAPUR UPH BAL DAPUR</t>
+  </si>
+  <si>
+    <t>KH TA K0N02U TAR MAINA DE VI BA0I0KA0 MAJAPUR UPH BAL DAPUR</t>
+  </si>
+  <si>
+    <t>KH TA K0N03U TAR MAINA DE VI BA0I0KA0 MAJAPUR UPH BAL DAPUR</t>
+  </si>
+  <si>
+    <t>KH TA K0N04U TAR !A0 PA0 !DHANACHAY MADHOPARU</t>
+  </si>
+  <si>
+    <t>!A0%V0 MADHOPARU BE SAK SH'A P(RASHAD K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 PA0 MADHOPARU K0NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0 PA0 MADHOPARU K0NAM0 3</t>
+  </si>
+  <si>
+    <t>!A0 PA0 MADHOPARU BE SAK SH'A P(RASHAD K0NAM0 3E</t>
+  </si>
+  <si>
+    <t>!A0 PA0 MADHOPARU BE SAK SH'A P(RASHAD K0NAM0 4</t>
+  </si>
+  <si>
+    <t>!A0 PA0 MADHOPARU K0NAM0 5</t>
+  </si>
+  <si>
+    <t>!A0 PA0 MADHOPARU K0NAM0 6</t>
+  </si>
+  <si>
+    <t>S T R%VADAS SAM0%V0MI DAR MADHOPUR</t>
+  </si>
+  <si>
+    <t>K0NAM0 1 S T R%VADAS SAM0%V0MI DAR MADHOPUR</t>
+  </si>
+  <si>
+    <t>K0NAM0 3 S T R%VADAS SAM0%V0MI DAR MADHOPUR</t>
+  </si>
+  <si>
+    <t>K0NAM0 4 DA,L -KATAB BASU NA JU0HA00KUL D(RAYACHAK</t>
+  </si>
+  <si>
+    <t>K0N0 1 DA,L -KATAB BASU NA JU0HA00KUL D(RAYACHAK</t>
+  </si>
+  <si>
+    <t>K0N0 2 DA,L -KATAB BASU NA JU0HA00KUL D(RAYACHAK</t>
+  </si>
+  <si>
+    <t>K0N0 3 DA,L -KATAB BASU NA JU0HA00KUL D(RAYACHAK</t>
+  </si>
+  <si>
+    <t>K0N0 4 DA,L -KATAB BASU NA JU0HA00KUL D(RAYACHAK</t>
+  </si>
+  <si>
+    <t>K0N0 5 DA,L -KATAB BASU NA JU0HA00KUL D(RAYACHAK</t>
+  </si>
+  <si>
+    <t>K0N0 6 DA,L -KATAB BASU NA JU0HA00KUL D(RAYACHAK</t>
+  </si>
+  <si>
+    <t>K0N0 7 DA,L -KATAB BASU NA JU0HA00KUL D(RAYACHAK</t>
+  </si>
+  <si>
+    <t>K0N0 8 DA,L -KATAB BASU NA JU0HA00KUL D(RAYACHAK</t>
+  </si>
+  <si>
+    <t>K0N0 9 SAR0VATI BA LAKA %V0 SUYAKU D SADHAR2PUR K0NAM0 1</t>
+  </si>
+  <si>
+    <t>SAR0VATI BA LAKA %V0 SUYAKU D SADHAR2PUR K0NAM0 2</t>
+  </si>
+  <si>
+    <t>SAR0VATI BA LAKA %V0 SUYAKU D SADHAR2PUR K0NAM0 3</t>
+  </si>
+  <si>
+    <t>SAR0VATI BA LAKA %V0 SUYAKU D SADHAR2PUR K0NAM0 4</t>
+  </si>
+  <si>
+    <t>SAR0VATI BA LAKA %V0 SUYAKU D SADHAR2PUR K0NAM0 5</t>
+  </si>
+  <si>
+    <t>SAR0VATI BA LAKA %V0 SUYAKU D SADHAR2PUR K0NAM0 6</t>
+  </si>
+  <si>
+    <t>SAR0VATI BA LAKA %V0 SUYAKU D SADHAR2PUR K0NAM0 7</t>
+  </si>
+  <si>
+    <t>SAR0VATI BA LAKA %V0 SUYAKU D SADHAR2PUR K0NAM0 8</t>
+  </si>
+  <si>
+    <t>ES0T20 3CH45EN EKEDAMI RASULAPUR K0 NAM0 1</t>
+  </si>
+  <si>
+    <t>ES0T20 3CH45EN EKEDAMI RASULAPUR K0 NAM0 2</t>
+  </si>
+  <si>
+    <t>ES0T20 3CH45EN EKEDAMI RASULAPUR K0 NAM0 3</t>
+  </si>
+  <si>
+    <t>ES0T20 3CH45EN EKEDAMI RASULAPUR K0 NAM0 4</t>
+  </si>
+  <si>
+    <t>MAULANA AJAD G4S IM0KA0 JA MAYANAGAR</t>
+  </si>
+  <si>
+    <t>RASALU PARU K0NAM0 1 MAULANA AJAD G4S IM0KA0 JA MAYANAGAR</t>
+  </si>
+  <si>
+    <t>RASALU PARU K0NAM0 2 MAULANA AJAD G4S IM0KA0 JA MAYANAGAR</t>
+  </si>
+  <si>
+    <t>RASALU PARU K0NAM0 3 MAULANA AJAD G4S IM0KA0 JA MAYANAGAR</t>
+  </si>
+  <si>
+    <t>RASALU PARU K0NAM0 4 MAULANA AJAD G4S IM0KA0 JA MAYANAGAR</t>
+  </si>
+  <si>
+    <t>RASALU PARU K0NAM0 5 MAHADE V !SAD SAMH JU0HA00KUL HUMAYUPUR</t>
+  </si>
+  <si>
+    <t>U TAR2 K0NAM01 MAHADE V !SAD SAMH JU0HA00KUL HUMAYUPUR</t>
+  </si>
+  <si>
+    <t>U TAR2 K0NAM02 MAHADE V !SAD SAMH JU0HA00KUL HUMAYUPUR</t>
+  </si>
+  <si>
+    <t>U TAR2 K0NAM03 MAHADE V !SAD SAMH JU0HA00KUL HUMAYUPUR</t>
+  </si>
+  <si>
+    <t>U TAR2 K0NAM04 LA0BA0SHA0JU0RE 0 I 0T29YUT HUMAYUPUR</t>
+  </si>
+  <si>
+    <t>K0NAM01 LA0BA0SHA0JU0RE 0 I 0T29YUT HUMAYUPUR</t>
+  </si>
+  <si>
+    <t>K0NAM02 LA0BA0SHA0JU0RE 0 I 0T29YUT HUMAYUPUR</t>
+  </si>
+  <si>
+    <t>K0NAM03 LA0BA0SHA0JU0RE 0 I 0T29YUT HUMAYUPUR</t>
+  </si>
+  <si>
+    <t>K0NAM04 LA0BA0SHA0JU0RE 0 I 0T29YUT HUMAYUPUR</t>
+  </si>
+  <si>
+    <t>K0NAM05 LA0BA0SHA0JU0RE 0 I 0T29YUT HUMAYUPUR</t>
+  </si>
+  <si>
+    <t>SHRCH0BBHDYAK06 |P0 |PTHABH0K0 BBHTNSHRCH|L|JBHDYAS THABHCHAKDYASCHABBHCHAJ SHRCH0BBHDYAK01</t>
+  </si>
+  <si>
+    <t>|P0 |PTHABH0K0 BBHTNSHRCH|L|JBHDYAS THABHCHAKDYASCHABBHCHAJ SHRCH0BBHDYAK02</t>
+  </si>
+  <si>
+    <t>SA0%V0MI DAR AL2NAGAR K0NAM0 1</t>
+  </si>
+  <si>
+    <t>SA0%V0MI DAR AL2NAGAR K0NAM0 2</t>
+  </si>
+  <si>
+    <t>SA0%V0MI DAR AL2NAGAR K0NAM0 3</t>
+  </si>
+  <si>
+    <t>SA0%V0MI DAR AL2NAGAR K0NAM0 4</t>
+  </si>
+  <si>
+    <t>SA0%V0MI DAR AL2NAGAR K0NAM0 5</t>
+  </si>
+  <si>
+    <t>SA0%V0MI DAR AL2NAGAR K0NAM0 6</t>
+  </si>
+  <si>
+    <t>DI0VI0IM0KALEJ JAPHARA BAJAR K0NAM01</t>
+  </si>
+  <si>
+    <t>DI0VI0IM0KALEJ JAPHARA BAJAR K0NAM02</t>
+  </si>
+  <si>
+    <t>DI0VI0IM0KALEJ JAPHARA BAJAR K0NAM03</t>
+  </si>
+  <si>
+    <t>DI0VI0IM0KALEJ JAPHARA BAJAR K0NAM04</t>
+  </si>
+  <si>
+    <t>DI0VI0IM0KALEJ JAPHARA BAJAR K0NAM05</t>
+  </si>
+  <si>
+    <t>DI0VI0IM0KALEJ JAPHARA BAJAR K0NAM06</t>
+  </si>
+  <si>
+    <t>DI0VI0IM0KALEJ JAPHARA BAJAR K0NAM07</t>
+  </si>
+  <si>
+    <t>DI0VI0IM0KALEJ JAPHARA BAJAR K0NAM08</t>
+  </si>
+  <si>
+    <t>DI0VI0IM0KALEJ JAPHARA BAJAR K0NAM09</t>
+  </si>
+  <si>
+    <t>DI0VI0IM0KALEJ JAPHARA BAJAR K0NAM010</t>
+  </si>
+  <si>
+    <t>DI0VI0IM0KALEJ JAPHARA BAJAR K0NAM011</t>
+  </si>
+  <si>
+    <t>DI0VI0IM0KALEJ JAPHARA BAJAR K0NAM012</t>
+  </si>
+  <si>
+    <t>MAHARANA !TAP JU0HA00KUL RAMAD TAPUR</t>
+  </si>
+  <si>
+    <t>HAL PAVU &gt; MAHARANA !TAP JU0HA00KUL RAMAD TAPUR</t>
+  </si>
+  <si>
+    <t>JBH|THABHKL|P THATHABHBBHS|THABHJBH|JBH|THABHKL|J~NADYABBH J~NAKL|JBH|THABHKL|SHRAKL|THATHABHKL !AIBHT|KL|THATHABH |PTHABHJDYABBH0JBH|THABHKL00AIBHTBBHDYABBH|P SHRAKL|J~NAKL|SHRCH AIBHT|KL|THATHABHBBH|SHR</t>
+  </si>
+  <si>
+    <t>HAL PAVU &gt; K0NAM03 MAHARANA !TAP JU0HA00KUL RAMAD TAPUR</t>
+  </si>
+  <si>
+    <t>JBH|THABHKL|P THATHABHBBHS|THABHJBH|JBH|THABHKL|J~NADYABBH AIBHTBBH0THATHABHKL|J~N04 J~NAKL|JBH|THABHKL|SHRAKL|THATHABHKL !AIBHT|KL|THATHABH |PTHABHJDYABBH0JBH|THABHKL00AIBHTBBHDYABBH|P SHRAKL|J~NAKL|SHRCH AIBHT|KL|THATHABHBBH|SHR</t>
+  </si>
+  <si>
+    <t>HAL K0NAM05 MAHARANA !TAP M@HALA MAHA%VAAYALAY RAMAD TAPUR</t>
+  </si>
+  <si>
+    <t>K0NAM01 MAHARANA !TAP M@HALA MAHA%VAAYALAY RAMAD TAPUR</t>
+  </si>
+  <si>
+    <t>K0NAM01E MAHARANA !TAP M@HALA MAHA%VAAYALAY RAMAD TAPUR</t>
+  </si>
+  <si>
+    <t>K0NAM02 MAHARANA !TAP M@HALA MAHA%VAAYALAY RAMAD TAPUR</t>
+  </si>
+  <si>
+    <t>K0NAM03 MAHARANA !TAP M@HALA MAHA%VAAYALAY RAMAD TAPUR</t>
+  </si>
+  <si>
+    <t>K0NAM04 MAHARANA !TAP M@HALA MAHA%VAAYALAY RAMAD TAPUR</t>
+  </si>
+  <si>
+    <t>K0NAM05 !A0 PA0 GHOSHIPARU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 PA0 GHOSHIPARU K0NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0 PA0 GHOSHIPARU K0NAM0 3</t>
+  </si>
+  <si>
+    <t>!A0 PA0 GHOSHIPARU K0NAM0 4</t>
+  </si>
+  <si>
+    <t>V. H0 3CH45EN EKEDAMI CTAVAR2PUR K0NAM0 1</t>
+  </si>
+  <si>
+    <t>V. H0 3CH45EN EKEDAMI CTAVAR2PUR K0NAM0 2</t>
+  </si>
+  <si>
+    <t>V. H0 3CH45EN EKEDAMI CTAVAR2PUR K0NAM0 3</t>
+  </si>
+  <si>
+    <t>V. H0 3CH45EN EKEDAMI CTAVAR2PUR K0NAM0 4</t>
+  </si>
+  <si>
+    <t>!A0 PA0 DYACU NASAPAL BOD ILAH2BAG K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 PA0 DYACU NASAPAL BOD ILAH2BAG K0NAM02</t>
+  </si>
+  <si>
+    <t>!A0 PA0 DYACU NASAPAL BOD ILAH2BAG K0NAM03</t>
+  </si>
+  <si>
+    <t>!A0 PA0 DYACU NASAPAL BOD ILAH2BAG K0NAM04</t>
+  </si>
+  <si>
+    <t>MAT U UJA HUSAIN HA0SE0 0KUL BHARAPURAVA GHASIKATARA K0NAM01</t>
+  </si>
+  <si>
+    <t>MAT U UJA HUSAIN HA0SE0 0KUL BHARAPURAVA GHASIKATARA K0NAM02</t>
+  </si>
+  <si>
+    <t>MAT U UJA HUSAIN HA0SE0 0KUL BHARAPURAVA GHASIKATARA K0NAM03</t>
+  </si>
+  <si>
+    <t>MAT U UJA HUSAIN HA0SE0 0KUL BHARAPURAVA GHASIKATARA K0NAM04</t>
+  </si>
+  <si>
+    <t>MAT U UJA HUSAIN HA0SE0 0KUL BHARAPURAVA GHASIKATARA K0NAM05</t>
+  </si>
+  <si>
+    <t>MAT U UJA HUSAIN HA0SE0 0KUL BHARAPURAVA GHASIKATARA K0NAM06</t>
+  </si>
+  <si>
+    <t>I0LA MAYA NASAR2 0KUL RAHAMATANAGAR K0NAM0 1</t>
+  </si>
+  <si>
+    <t>I0LA MAYA NASAR2 0KUL RAHAMATANAGAR @TAN SHED</t>
+  </si>
+  <si>
+    <t>I0LA MAYA NASAR2 0KUL RAHAMATANAGAR K0NAM0 2</t>
+  </si>
+  <si>
+    <t>I0LA MAYA NASAR2 0KUL RAHAMATANAGAR K0NAM0 3</t>
+  </si>
+  <si>
+    <t>I0LA MAYA NASAR2 0KUL RAHAMATANAGAR K0NAM0 4</t>
+  </si>
+  <si>
+    <t>I0LA MAYA NASAR2 0KUL RAHAMATANAGAR K0NAM0 5</t>
+  </si>
+  <si>
+    <t>I0LA MAYA NASAR2 0KUL RAHAMATANAGAR K0NAM0 6</t>
+  </si>
+  <si>
+    <t>MARAVAD IM0 KA0 I0MAILAPUR NASIRABAD</t>
+  </si>
+  <si>
+    <t>K0NAM0 2 MARAVAD IM0 KA0 I0MAILAPUR NASIRABAD</t>
+  </si>
+  <si>
+    <t>K0NAM0 3 MARAVAD IM0 KA0 I0MAILAPUR NASIRABAD</t>
+  </si>
+  <si>
+    <t>K0NAM0 4 MARAVAD IM0 KA0 I0MAILAPUR NASIRABAD</t>
+  </si>
+  <si>
+    <t>K0NAM0 5 MARAVAD IM0 KA0 I0MAILAPUR NASIRABAD</t>
+  </si>
+  <si>
+    <t>K0NAM0 6 MARAVAD IM0 KA0 I0MAILAPUR NASIRABAD</t>
+  </si>
+  <si>
+    <t>K0NAM0 7 MARAVAD IM0 KA0 I0MAILAPUR NASIRABAD</t>
+  </si>
+  <si>
+    <t>K0NAM0 8 MARAVAD IM0 KA0 I0MAILAPUR NASIRABAD</t>
+  </si>
+  <si>
+    <t>K0NAM0 9 MARAVAD IM0 KA0 I0MAILAPUR NASIRABAD</t>
+  </si>
+  <si>
+    <t>K0NAM0 10 MARAVAD IM0 KA0 I0MAILAPUR NASIRABAD</t>
+  </si>
+  <si>
+    <t>K0NAM0 11 MARAVAD IM0 KA0 I0MAILAPUR NASIRABAD</t>
+  </si>
+  <si>
+    <t>K0NAM0 12 MARAVAD IM0 KA0 I0MAILAPUR NASIRABAD</t>
+  </si>
+  <si>
+    <t>K0NAM0 13 RAMADE I K YA IM0KA0 D2VAN BAJAR K0NAM0 1</t>
+  </si>
+  <si>
+    <t>RAMADE I K YA IM0KA0 D2VAN BAJAR K0NAM0 2</t>
+  </si>
+  <si>
+    <t>RAMADE I K YA IM0KA0 D2VAN BAJAR K0NAM0 3</t>
+  </si>
+  <si>
+    <t>RAMADE I K YA IM0KA0 D2VAN BAJAR K0NAM0 4</t>
+  </si>
+  <si>
+    <t>RAMADE I K YA IM0KA0 D2VAN BAJAR K0NAM0 5</t>
+  </si>
+  <si>
+    <t>RAMADE I K YA IM0KA0 D2VAN BAJAR K0NAM0 6</t>
+  </si>
+  <si>
+    <t>DI0VI0IM0KALEJ B:SHIPARU K0NAM0 1 MUGTIPUR</t>
+  </si>
+  <si>
+    <t>DI0VI0IM0KALEJ B:SHIPARU K0NAM0 2 MUGTIPUR</t>
+  </si>
+  <si>
+    <t>DI0VI0IM0KALEJ B:SHIPARU K0NAM0 3 MUGTIPUR</t>
+  </si>
+  <si>
+    <t>DI0VI0IM0KALEJ B:SHIPARU K0NAM0 4 MUGTIPUR</t>
+  </si>
+  <si>
+    <t>DI0VI0IM0KALEJ B:SHIPARU K0NAM0 5 MUGTIPUR</t>
+  </si>
+  <si>
+    <t>AMJUMAN I0LA MAYA 0KUL KHUNIPUR K0NAM0 1</t>
+  </si>
+  <si>
+    <t>AMJUMAN I0LA MAYA 0KUL KHUNIPUR K0NAM0 2</t>
+  </si>
+  <si>
+    <t>AMJUMAN I0LA MAYA 0KUL KHUNIPUR K0NAM0 3</t>
+  </si>
+  <si>
+    <t>AMJUMAN I0LA MAYA 0KUL KHUNIPUR K0NAM0 4</t>
+  </si>
+  <si>
+    <t>AMJUMAN I0LA MAYA 0KUL KHUNIPUR K0NAM0 5</t>
+  </si>
+  <si>
+    <t>AMJUMAN I0LA MAYA 0KUL KHUNIPUR K0NAM0 6</t>
+  </si>
+  <si>
+    <t>AMJUMAN I0LA MAYA 0KUL KHUNIPUR K0NAM0 7</t>
+  </si>
+  <si>
+    <t>JDYAIBHTDYASHRCH|L|S 0BBHDY|PTHABH CH0SHRCHADY0 JBHDY|P SHRADYABBHCHAJ SHRCH|THABHDY|P SHRCH0BBHDYAK0 10</t>
+  </si>
+  <si>
+    <t>JDYAIBHTDYASHRCH|L|S 0BBHDY|PTHABH CH0SHRCHADY0 JBHDY|P SHRADYABBHCHAJ SHRCH|THABHDY|P SHRCH0BBHDYAK0 11</t>
+  </si>
+  <si>
+    <t>JDYAIBHTDYASHRCH|L|S 0BBHDY|PTHABH CH0SHRCHADY0 JBHDY|P SHRADYABBHCHAJ SHRCH|THABHDY|P SHRCH0BBHDYAK0 12</t>
+  </si>
+  <si>
+    <t>TULASIDAS IHTAR KALOJ GORAKHAPUR K0NAM05</t>
+  </si>
+  <si>
+    <t>TULASIDAS IHTAR KALOJ GORAKHAPUR K0NAM06</t>
+  </si>
+  <si>
+    <t>TULASIDAS IHTAR KALOJ GORAKHAPUR K0NAM07</t>
+  </si>
+  <si>
+    <t>TULASIDAS IHTAR KALOJ GORAKHAPUR K0NAM08</t>
+  </si>
+  <si>
+    <t>TULASIDAS IHTAR KALOJ GORAKHAPUR K0NAM09</t>
+  </si>
+  <si>
+    <t>TULASIDAS IHTAR KALOJ GORAKHAPUR K0NAM10</t>
+  </si>
+  <si>
+    <t>TULASIDAS IHTAR KALOJ GORAKHAPUR K0NAM11</t>
+  </si>
+  <si>
+    <t>TULASIDAS IHTAR KALOJ GORAKHAPUR K0NAM12</t>
+  </si>
+  <si>
+    <t>TULASIDAS IHTAR KALOJ GORAKHAPUR K0NAM13</t>
+  </si>
+  <si>
+    <t>!A0%V0RAUTAPATHASHALA TUKAMANAPUR K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0%V0RAUTAPATHASHALA TUKAMANAPUR K0NAM02</t>
+  </si>
+  <si>
+    <t>PU0MA0%V0RAUTAPATHASHALA TUKAMANAPUR K0NAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0%V0RAUTAPATHASHALA TUKAMANAPUR K0NAM0 2</t>
+  </si>
+  <si>
+    <t>SAM0KRRIT PATHASHALA TUKAMANAPUR K0NAM01</t>
+  </si>
+  <si>
+    <t>SAM0KRRIT PATHASHALA TUKAMANAPUR K0NAM02</t>
+  </si>
+  <si>
+    <t>SAM0KRRIT PATHASHALA TUKAMANAPUR K0NAM03</t>
+  </si>
+  <si>
+    <t>SAM0KRRIT PATHASHALA TUKAMANAPUR K0NAM04</t>
+  </si>
+  <si>
+    <t>SAM0KRRIT PATHASHALA TUKAMANAPUR K0NAM05</t>
+  </si>
+  <si>
+    <t>TULASIDAS IM0KA0 GORAKHAPARU KAM0 NAM0 14</t>
+  </si>
+  <si>
+    <t>TULASIDAS IM0KA0 GORAKHAPARU KAM0 NAM0 15</t>
+  </si>
+  <si>
+    <t>TULASIDAS IM0KA0 GORAKHAPARU KAM0 NAM0 16</t>
+  </si>
+  <si>
+    <t>TULASIDAS IM0KA0 GORAKHAPARU KAM0 NAM0 17</t>
+  </si>
+  <si>
+    <t>BAL BAHAR NASAR2 0KUL BAS TAPUR K0NAM0 1</t>
+  </si>
+  <si>
+    <t>BAL BAHAR NASAR2 0KUL BAS TAPUR K0NAM0 2</t>
+  </si>
+  <si>
+    <t>BAL BAHAR NASAR2 0KUL BAS TAPUR K0NAM0 3</t>
+  </si>
+  <si>
+    <t>BAL BAHAR NASAR2 0KUL BAS TAPUR K0NAM0 4</t>
+  </si>
+  <si>
+    <t>BAL BAHAR NASAR2 0KUL BAS TAPUR K0NAM0 5</t>
+  </si>
+  <si>
+    <t>I0V TE N 0KUL MAJAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>I0V TE N 0KUL MAJAPARU K0NAM02</t>
+  </si>
+  <si>
+    <t>I0V TE N 0KUL MAJAPARU K0NAM03</t>
+  </si>
+  <si>
+    <t>I0V TE N 0KUL MAJAPARU K0NAM04</t>
+  </si>
+  <si>
+    <t>I0V TE N 0KUL MAJAPARU K0NAM05</t>
+  </si>
+  <si>
+    <t>I0V TE N 0KUL MAJAPARU K0NAM06</t>
+  </si>
+  <si>
+    <t>SHRAKL|PTHABHJKL|AIBHTBBHDYASDYAI 0THATHABHKLDYACHJBH|THABH BBH AIBHT|KL|SHR AIBHTBBH|KL|PK|PTHABHJ |PKL|PKL|SHRCH|BBHAIBHTBBHDYAIDYABBH AIDYAJ0</t>
+  </si>
+  <si>
+    <t>AIBHTBBH0THATHABHKL|J~N01 SHRAKL|PTHABHJKL|AIBHTBBHDYASDYAI 0THATHABHKLDYACHJBH|THABH BBH AIBHT|KL|SHR AIBHTBBH|KL|PK|PTHABHJ |PKL|PKL|SHRCH|BBHAIBHTBBHDYAIDYABBH AIDYAJ0</t>
+  </si>
+  <si>
+    <t>AIBHTBBH0THATHABHKL|J~N02 SHRAKL|PTHABHJKL|AIBHTBBHDYASDYAI 0THATHABHKLDYACHJBH|THABH BBH AIBHT|KL|SHR AIBHTBBH|KL|PK|PTHABHJ |PKL|PKL|SHRCH|BBHAIBHTBBHDYAIDYABBH AIDYAJ0</t>
+  </si>
+  <si>
+    <t>AIBHTBBH0THATHABHKL|J~N03 SHRAKL|PTHABHJKL|AIBHTBBHDYASDYAI 0THATHABHKLDYACHJBH|THABH BBH AIBHT|KL|SHR AIBHTBBH|KL|PK|PTHABHJ |PKL|PKL|SHRCH|BBHAIBHTBBHDYAIDYABBH AIDYAJ0</t>
+  </si>
+  <si>
+    <t>AIBHTBBH0THATHABHKL|J~N04 SHRAKL|PTHABHJKL|AIBHTBBHDYASDYAI 0THATHABHKLDYACHJBH|THABH BBH AIBHT|KL|SHR AIBHTBBH|KL|PK|PTHABHJ |PKL|PKL|SHRCH|BBHAIBHTBBHDYAIDYABBH AIDYAJ0</t>
+  </si>
+  <si>
+    <t>AIBHTBBH0THATHABHKL|J~N05 SHRAKL|PTHABHJKL|AIBHTBBHDYASDYAI 0THATHABHKLDYACHJBH|THABH BBH AIBHT|KL|SHR AIBHTBBH|KL|PK|PTHABHJ |PKL|PKL|SHRCH|BBHAIBHTBBHDYAIDYABBH AIDYAJ0</t>
+  </si>
+  <si>
+    <t>AIBHTBBH0THATHABHKL|J~N07 SHRAKL|PTHABHJKL|AIBHTBBHDYASDYAI 0THATHABHKLDYACHJBH|THABH BBH AIBHT|KL|SHR AIBHTBBH|KL|PK|PTHABHJ |PKL|PKL|SHRCH|BBHAIBHTBBHDYAIDYABBH AIDYAJ0</t>
+  </si>
+  <si>
+    <t>AIBHTBBH0THATHABHKL|J~N08 SHRAKL|PTHABHJKL|AIBHTBBHDYASDYAI 0THATHABHKLDYACHJBH|THABH BBH AIBHT|KL|SHR AIBHTBBH|KL|PK|PTHABHJ |PKL|PKL|SHRCH|BBHAIBHTBBHDYAIDYABBH AIDYAJ0</t>
+  </si>
+  <si>
+    <t>K0NAM09 !A0PA0THANA RAJAGHAT KE PICHE K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0PA0THANA RAJAGHAT KE PICHE K0NAM02</t>
+  </si>
+  <si>
+    <t>!A0 PA0 MADARASA CHAURAHA BAS TAPUR K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 PA0 MADARASA CHAURAHA BAS TAPUR K0NAM02</t>
+  </si>
+  <si>
+    <t>AMANA G4S IM0KA0BAHARAMAPUR K0NAM01</t>
+  </si>
+  <si>
+    <t>AMANA G4S IM0KA0BAHARAMAPUR K0NAM02</t>
+  </si>
+  <si>
+    <t>AMANA G4S IM0KA0BAHARAMAPUR K0NAM03</t>
+  </si>
+  <si>
+    <t>AMANA G4S IM0KA0BAHARAMAPUR K0NAM04</t>
+  </si>
+  <si>
+    <t>AMANA MU0 G4S IM0KA0BAHARAMAPUR U TAR2</t>
+  </si>
+  <si>
+    <t>BHAG K0NAM06 AMANA MU0 G4S IM0KA0BAHARAMAPUR U TAR2</t>
+  </si>
+  <si>
+    <t>BHAG K0NAM07 AMANA MU0 G4S IM0KA0BAHARAMAPUR U TAR2</t>
+  </si>
+  <si>
+    <t>BHAG K0NAM08 AMANA MU0 G4S IM0KA0BAHARAMAPUR U TAR2</t>
+  </si>
+  <si>
+    <t>BHAG K0NAM09 AMANA G4S IM0 KA0 BAHARAMAPUR K0NAM0 10</t>
+  </si>
+  <si>
+    <t>!A0 PA0 BAHARAMAPARU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 PA0 SHERAGADH</t>
+  </si>
+  <si>
+    <t>ADASH JANATA I TAR KALEJ NAUSADH K0NAM0 1</t>
+  </si>
+  <si>
+    <t>ADASH JANATA I TAR KALEJ NAUSADH K0NAM0 2</t>
+  </si>
+  <si>
+    <t>ADASH JANATA I TAR KALEJ NAUSADH K0NAM0 3</t>
+  </si>
+  <si>
+    <t>ADASH JANATA I TAR KALEJ NAUSADH K0NAM0 4</t>
+  </si>
+  <si>
+    <t>ADASH JANATA I TAR KALEJ NAUSADH K0NAM0 5</t>
+  </si>
+  <si>
+    <t>ADASH JANATA I TAR KALEJ NAUSADH K0NAM0 6</t>
+  </si>
+  <si>
+    <t>ADASH JANATA I TAR KALEJ NAUSADH K0NAM0 7</t>
+  </si>
+  <si>
+    <t>!A0 PA0 BHALORA KHAD U K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 PA0 BHALORA KHAD U K0NAM02</t>
+  </si>
+  <si>
+    <t>!A0 PA0 HARAI YA K0 NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 PA0 HARAI YA K0 NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0 PA0 GARU AUL2 BU0 K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 PA0 CH%PAYA K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0HA00KUL CH%PAYA K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 PA0 PEVANAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 PA0 A@HARAUL2 PATAKHAIL2 K0NAM0 1</t>
+  </si>
+  <si>
+    <t>PAMCHAYATABHAVAN EKALA</t>
+  </si>
+  <si>
+    <t>!A0 PA0 %PAPAR2 K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 PA0 BETAUVA UPH CHANAU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 PA0 BETAUVA UPH CHANAU K0NAM0 2</t>
+  </si>
+  <si>
+    <t>PAMCHAYATABHAVAN BAGHAGADA K0NAM01</t>
+  </si>
+  <si>
+    <t>RA0 HODYOPAI3THAK 3CH-K YALAY BAGHAGADA</t>
+  </si>
+  <si>
+    <t>PAMCHAYATABHAVAN BAGHAGADA K0NAM02</t>
+  </si>
+  <si>
+    <t>PAMCHAYATABHAVAN BAGHAGADA K0NAM03</t>
+  </si>
+  <si>
+    <t>!A0 PA0 BAGHAGADA(JITAPARU ) K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 PA0 TALANAVAR K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 PA0 TALANAVAR K0NAM02</t>
+  </si>
+  <si>
+    <t>!A0 PA0 A@HARAUL2 K0 NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 PA0 A@HARAUL2 K0 NAM0 2</t>
+  </si>
+  <si>
+    <t>SAMAD U ACYAK %VAKAS KE O K0NAM0 1</t>
+  </si>
+  <si>
+    <t>SAMAD U ACYAK %VAKAS KE O K0NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0 PA0 KALANI BAJ U UG K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 PA0 KALANI KHAD U K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 PA0 PYOH(RAYA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 PA0 PYOH(RAYA K0NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0 PA0 UCHAGAMV K0 NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 PA0 JOTADADAVA K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 PA0 SEVAI K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 PA0 SEVAI K0NAM02</t>
+  </si>
+  <si>
+    <t>PAMCHAYATABHAVAN SEVAI K0NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0 PA0 SEVAI K0NAM03</t>
+  </si>
+  <si>
+    <t>!A0 PA0 KAKARAKHOR K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 PA0 KAKARAKHOR K0NAM02</t>
+  </si>
+  <si>
+    <t>!A0 %V0 AKHALASAKAMU VAR K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 %V0 AKHALASAKAMU VAR K0NAM02</t>
+  </si>
+  <si>
+    <t>!A0 %V0 AKHALASAKAMU VAR K0NAM03</t>
+  </si>
+  <si>
+    <t>!A0 %V0 DEPHARA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 %V0 DEPHARA K0NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0 PA0 JAMGAL %VAQAMAPARU</t>
+  </si>
+  <si>
+    <t>!A0 PA0 JAM0 D2GHAN SAMH K0NAM02</t>
+  </si>
+  <si>
+    <t>MAH2P NARAYAN SHAH2 IM0KA0 JAM0 RANI SOHAS KUMVAR2</t>
+  </si>
+  <si>
+    <t>K0NAM01 MAH2P NARAYAN SHAH2 IM0KA0 JAM0 RANI SOHAS KUMVAR2</t>
+  </si>
+  <si>
+    <t>K0NAM02 MAH2P NARAYAN SHAH2 IM0KA0 JAM0 RANI SOHAS KUMVAR2</t>
+  </si>
+  <si>
+    <t>K0NAM04 !A0PA0 MAHAVIR CHAPARA JAM0 RANI SOHAS KUMVAR2 K0 NAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0%V0 JUDAPARU JAM0 RANI SOHAS KUMVAR2 K0N0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0%V0 BADERDAYA JAM0 RANI SOHAS KUMVAR2 K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 PA0 JUDAPARU JAM0 RANI SOHAS KUMVAR2 K0 NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 PA0 JUDAPARU JAM0 RANI SOHAS KUMVAR2 K0 NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0 PA0 QIPARU A JAM0 RANI SOHAS KUMVAR2 K0NAM0 1</t>
+  </si>
+  <si>
+    <t>S0P0 TOTAHA UPH BHAUVAPAR K0NAM0 1</t>
+  </si>
+  <si>
+    <t>S0P0 TOTAHA UPH BHAUVAPAR K0NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0 PA0 TOTAHA UPH BHAUVAPAR K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 PA0 TOTAHA UPH BHAUVAPAR K0NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0 PA0 TOTAHA UPH BHAUVAPAR K0NAM0 3</t>
+  </si>
+  <si>
+    <t>!A0 PA0 BALAI U GADA</t>
+  </si>
+  <si>
+    <t>!A0 PA0 JOT KHAIRA K0 NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 PA0 CHE(RAYA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 PA0 JOT BAGAH2 U TAR2 K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 PA0 JOT BAGAH2 DAS'NI K0NAM02</t>
+  </si>
+  <si>
+    <t>KAYALAY KRRI%SH U PADAN MAHDI MAHE VA K0NAM01</t>
+  </si>
+  <si>
+    <t>KAYALAY KRRI%SH U PADAN MAHDI MAHE VA K0NAM02</t>
+  </si>
+  <si>
+    <t>KAYALAY KRRI%SH U PADAN MAHDI MAHE VA K0NAM03</t>
+  </si>
+  <si>
+    <t>KAYALAY KRRI%SH U PADAN MAHDI MAHE VA K0NAM04</t>
+  </si>
+  <si>
+    <t>!A0 %V0 JHARAVA K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 %V0 JHARAVA K0NAM02</t>
+  </si>
+  <si>
+    <t>!A0%V0 SEMARADE VI !SAD K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0%V0 SEMARADE VI !SAD K0NAM02</t>
+  </si>
+  <si>
+    <t>!A0%V0 SEMARADE VI !SAD K0NAM03</t>
+  </si>
+  <si>
+    <t>!A0 %V0 BADAGAU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 %V0 BADAGAU K0NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0 %V0 BADAGAU K0NAM0 3</t>
+  </si>
+  <si>
+    <t>!A0 %V0 BADAGAU K0NAM0 4</t>
+  </si>
+  <si>
+    <t>!A0 %V0 BADAGAU K0NAM0 5</t>
+  </si>
+  <si>
+    <t>!A0 %V0 MAMJH(RAYA B0TAUL K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 %V0 MAMJH(RAYA B0TAUL K0NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0%V0 SE DAL U 2 BE DAL U 2 K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 %V0 LAHASADI K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 %V0 LAHASADI K0NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0 %V0 LAHASADI K0NAM0 3</t>
+  </si>
+  <si>
+    <t>!A0 %V0 LAHASADI K0NAM0 4</t>
+  </si>
+  <si>
+    <t>!A0 %V0 LAHASADI K0NAM0 5</t>
+  </si>
+  <si>
+    <t>!A0 %V0 KAJAKAPARU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 %V0 KAJAKAPARU K0NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0 %V0 KAJAKAPARU K0NAM0 3</t>
+  </si>
+  <si>
+    <t>KRRIVNAKUMAR KANORDAYA JANATA %VAAYALAY</t>
+  </si>
+  <si>
+    <t>MAHUISAGH U RAPARU K0NAM01 KRRIVNAKUMAR KANORDAYA JANATA %VAAYALAY</t>
+  </si>
+  <si>
+    <t>MAHUISAGH U RAPARU K0NAM02 KRRIVNAKUMAR KANORDAYA JANATA %VAAYALAY</t>
+  </si>
+  <si>
+    <t>MAHUISAGH U RAPARU K0NAM03 NAV4S NESHANAL EKEDAMI PHULAV(RAYA MAHUISUGHARAPUR</t>
+  </si>
+  <si>
+    <t>K0NAM0 1 NAV4S NESHANAL EKEDAMI PHULAV(RAYA MAHUISUGHARAPUR</t>
+  </si>
+  <si>
+    <t>MAHUISAGH U RAPARU K0NAM04 KRRIVNAKUMAR KANORDAYA JANATA %VAAYALAY</t>
+  </si>
+  <si>
+    <t>MAHUISAGH U RAPARU K0NAM05 KRRIVNAKUMAR KANORDAYA JANATA %VAAYALAY</t>
+  </si>
+  <si>
+    <t>MAHUISAGHU RAPARU K0NAM06 !A0 %V0 BHARAV LAYA BAJ U UG K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 %V0 BHARAV LAYA BAJ U UG K0NAM02</t>
+  </si>
+  <si>
+    <t>!A0 %V0 BHARAV LAYA BAJ U UG K0NAM03</t>
+  </si>
+  <si>
+    <t>PAMCHAYATABHAVAN BHARAV LAYA BUJUG K0NAM01</t>
+  </si>
+  <si>
+    <t>PU0MA0%V0 PATHARA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0%V0 PATHARA K0NAM0 2</t>
+  </si>
+  <si>
+    <t>GO0 PIWLAK 0KUL BAGARANI K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 %V0 GAYAGHAT KHAD U K0 NAM01</t>
+  </si>
+  <si>
+    <t>!A0 %V0 GAYAGHAT KHAD U K0 NAM02</t>
+  </si>
+  <si>
+    <t>!A0 %V0 GAYAGHAT BAJ U UG K0NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0 %V0 RAMAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 %V0 RAMAPARU K0NAM02</t>
+  </si>
+  <si>
+    <t>!A0 %V0 JAM0 RAMAGADH UPH RAJAH2 K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 %V0 JAM0 RAMAGADH UPH RAJAH2 K0NAM0 2</t>
+  </si>
+  <si>
+    <t>JU0 HA0 0KUL JAM0 RAMAGADH UPH RAJAH2 K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0 HA0 0KUL JAM0 RAMAGADH UPH RAJAH2K0NAM02</t>
+  </si>
+  <si>
+    <t>!A0 %V0 KHORABAR UPH SUBABAJAR K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 %V0 KHORABAR UPH SUBABAJAR K0NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0 %V0 KHORABAR UPH SUBABAJAR K0NAM0 3</t>
+  </si>
+  <si>
+    <t>PU0 MA0 %V0 KHORABAR UPH SUBABAJAR K0NAM01</t>
+  </si>
+  <si>
+    <t>PAMCHAYATABHAVAN KHORABAR UPH SUBABAJAR K0NAM01</t>
+  </si>
+  <si>
+    <t>PAMCHAYATABHAVAN KHORABAR UPH SUBABAJAR K0NAM02</t>
+  </si>
+  <si>
+    <t>!A0%V0 S:TAUR K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0%V0 S:TAUR K0NAM02</t>
+  </si>
+  <si>
+    <t>!A0%V0 S:TAUR K0NAM03</t>
+  </si>
+  <si>
+    <t>DAYAN D IM0KA0 JAM0 SAKAR2 UPH KHORABAR</t>
+  </si>
+  <si>
+    <t>K0NAM01 DAYAN D IM0KA0 JAM0 SAKAR2 UPH KHORABAR</t>
+  </si>
+  <si>
+    <t>K0NAM02 DAYAN D IM0KA0 JAM0 SAKAR2 UPH KHORABAR</t>
+  </si>
+  <si>
+    <t>K0NAM03 DAYAN D IM0KA0 JAM0 SAKAR2 UPH KHORABAR</t>
+  </si>
+  <si>
+    <t>K0NAM04 DAYAN D IM0KA0 JAM0 SAKAR2 UPH KHORABAR</t>
+  </si>
+  <si>
+    <t>K0NAM05 !A0 %V0 TAL K DALA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0%V0 JAM0 AYOXYA!SAD KAM0 NAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0%V0JAM0 AYOXYA !SAD K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 %V0 M@HAMATH K0NAM0 1</t>
+  </si>
+  <si>
+    <t>JU0HA00KUL BABHANI K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0HA00KUL BABHANI K0NAM02</t>
+  </si>
+  <si>
+    <t>!A0%V0 SAHUKOL UPH MAJAPUR K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0%V0 DAMGIPAR K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0%V0 DAMGIPAR K0NAM02</t>
+  </si>
+  <si>
+    <t>!A0%V0 DAMGIPAR K0NAM03</t>
+  </si>
+  <si>
+    <t>!A0%V0 H:KABAD K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 %V0 KONI K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0%V0PATAPAR K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0%V0PATAPAR K0NAM02</t>
+  </si>
+  <si>
+    <t>JU0 HA0 0KUL LALAPARU T2KAR K0NAM0 1</t>
+  </si>
+  <si>
+    <t>JU0 HA0 0KUL LALAPARU T2KAR K0NAM0 2</t>
+  </si>
+  <si>
+    <t>JU0 HA0 0KUL LALAPARU T2KAR K0NAM0 3</t>
+  </si>
+  <si>
+    <t>JU0 HA0 0KUL LALAPARU T2KAR K0NAM0 4</t>
+  </si>
+  <si>
+    <t>PAMCHAYATABHAVAN DU@HAYA K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 %V0 %VASHUNAPARU BU0</t>
+  </si>
+  <si>
+    <t>PAMCHAYATABHAVAN SANAHA K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 %V0 SANAHA K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAPHA K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0%V0 %VASHUNAPARU KHAD U K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0 HA0 0KUL JAM0 RAMAGADH UPH CHAVAR2K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0 HA0 0KUL JAM0 RAMAGADH UPH CHAVAR2K0NAM02</t>
+  </si>
+  <si>
+    <t>JU0 HA0 0KUL JAM0 RAMAGADH UPH CHAVAR2K0NAM03</t>
+  </si>
+  <si>
+    <t>JU0 HA0 0KUL JAM0 RAMAGADH UPH CHAVAR2K0NAM04</t>
+  </si>
+  <si>
+    <t>!A0%V0 JAM0 RAMAGADH UPH CHAMVAR2 K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0%V0 JAM0 RAMAGADH UPH CHAMVAR2 K0NAM02</t>
+  </si>
+  <si>
+    <t>!A0%V0 RAYAGAMJ K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0%V0 RAYAGAMJ K0NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0%V0 RAYAGAMJ K0NAM0 3</t>
+  </si>
+  <si>
+    <t>PU0MA0%V0RAYAGAMJ K0NAM01</t>
+  </si>
+  <si>
+    <t>PU0MA0%V0RAYAGAMJ K0NAM02</t>
+  </si>
+  <si>
+    <t>ADASH I0KA0 JAM0 BELAVAR U TAR K0NAM01</t>
+  </si>
+  <si>
+    <t>ADASH I0KA0 JAM0 BELAVAR U TAR K0NAM02</t>
+  </si>
+  <si>
+    <t>!A0 %V0 JAM0 KEVAT LAYA PURAB K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!DY0RUJ0 AIBHTDYAK0 SHRCH|DAJDYASHR AIDYASDY BBHCHLABHTHATHABHDYAK|CH SHRCH0BBHDYAK02</t>
+  </si>
+  <si>
+    <t>!A0 %V0 JAM0 RAMALAKHANA PURAB K0NAM01</t>
+  </si>
+  <si>
+    <t>!DY0RUJ0 AIBHTDYAK0 JDYAKDYAIDYASHRCH|THABHDYABBHDY BBHCHLABHTHATHABHDYAK|CH SHRCH0BBHDYAK02</t>
+  </si>
+  <si>
+    <t>!A0 %V0 JAM0 RAMALAKHANA U TAR K0NAM03</t>
+  </si>
+  <si>
+    <t>PU0MA0%V0 TARAKULAH2 K0NAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0%V0 TARAKULAH2 K0NAM0 2</t>
+  </si>
+  <si>
+    <t>PU0MA0%V0 TARAKULAH2 K0NAM0 3</t>
+  </si>
+  <si>
+    <t>PU0MA0%V0 TARAKULAH2 K0NAM0 4</t>
+  </si>
+  <si>
+    <t>!A0 %V0 POCCHAYA YDH0THAN K0 NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 %V0 POCCHAYA YDH0THAN K0 NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0 %V0 RAMAPARU K0 NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 %V0 RAMAPARU K0 NAM0 2</t>
+  </si>
+  <si>
+    <t>PU0MA0%V0 RAMAPARU K0NAM03</t>
+  </si>
+  <si>
+    <t>!A0 %V0 AZDA MOTIRAM KAV NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 %V0 AZDA MOTIRAM KAV NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0 %V0 AZDA MOTIRAM KAV NAM0 3</t>
+  </si>
+  <si>
+    <t>!A0 %V0 AZDA MOTIRAM KAV NAM0 4</t>
+  </si>
+  <si>
+    <t>!A0 %V0 SHAVAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 %V0 SHAVAPARU K0NAM02</t>
+  </si>
+  <si>
+    <t>!A0 %V0 G@HARA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 %V0 G@HARA K0NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0 %V0 G@HARA K0NAM0 3</t>
+  </si>
+  <si>
+    <t>K YA !A0 %V0 G@HARA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>K YA !A0 %V0 G@HARA K0NAM0 2</t>
+  </si>
+  <si>
+    <t>K YA !A0 %V0 G@HARA K0NAM0 3</t>
+  </si>
+  <si>
+    <t>!A0 %V0 SONAVE K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 %V0 SONAVE K0NAM02</t>
+  </si>
+  <si>
+    <t>EK K'IY BHAVAN !A0%V0 SONAVE K0NAM3</t>
+  </si>
+  <si>
+    <t>EK K'IY BHAVAN !A0%V0 SONAVE K0NAM4</t>
+  </si>
+  <si>
+    <t>!A0 %V0 AKOLAH2 K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0 %V0 AKOLAH2 K0NAM02</t>
+  </si>
+  <si>
+    <t>PHALADASE TAR NAUVA APVAL K0NAM0 1</t>
+  </si>
+  <si>
+    <t>PHALADASE TAR NAUVA APVAL K0NAM0 2</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT BHAVAN DUMAR2 K0 NAM0 1</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT BHAVAN DUMAR2 K0 NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0%V0 GAUR2 MAMGALAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>!A0%V0 GAUR2 MAMGALAPARU K0NAM02</t>
+  </si>
+  <si>
+    <t>!A0 %V0 GAUR K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAPARA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>JU0HA00KUL SEMARA MACNAK CHAUK PURAB K0NAM0 1</t>
+  </si>
+  <si>
+    <t>JU0HA00KUL SEMARA MACNAK CHAUK PURAB K0NAM0 2</t>
+  </si>
+  <si>
+    <t>!KL0TNSHR0 SHRCH|THABHAIKLDYACHBBH AIBHTBBH0THATHABHKL|J~N01</t>
+  </si>
+  <si>
+    <t>SADHAN SAHAKAR2 S MACT KUI K0NAM0 1</t>
+  </si>
+  <si>
+    <t>SADHAN SAHAKAR2 S MACT KUI K0NAM0 2</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM NO. 423</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM NO. 424</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM NO. 425</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM NO. 426</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM NO. 427</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM NO. 428</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 429</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 430</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 431</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 432</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 433</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 434</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 435</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 436</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 437</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 438</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 439</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 440</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 441</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 442</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 443</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 444</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 445</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 446</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 447</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 448</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 449</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 450</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 451</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 452</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 453</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 454</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 455</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 456</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 457</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 458</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 459</t>
+  </si>
+  <si>
+    <t>!A0 %V0 CHAKADE IYA K0NAM0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 460</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -1349,8 +1541,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1366,7 +1566,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1374,12 +1574,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1678,94 +1896,175 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:28">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:28">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>418</v>
+        <v>482</v>
       </c>
       <c r="D2" t="s">
-        <v>419</v>
+        <v>483</v>
       </c>
       <c r="E2" t="s">
-        <v>420</v>
+        <v>484</v>
       </c>
       <c r="F2" t="s">
-        <v>421</v>
+        <v>485</v>
       </c>
       <c r="G2" t="s">
-        <v>422</v>
+        <v>486</v>
       </c>
       <c r="H2" t="s">
-        <v>423</v>
+        <v>487</v>
       </c>
       <c r="I2" t="s">
-        <v>424</v>
+        <v>488</v>
       </c>
       <c r="J2" t="s">
-        <v>425</v>
+        <v>489</v>
       </c>
       <c r="K2" t="s">
-        <v>426</v>
+        <v>490</v>
       </c>
       <c r="L2" t="s">
-        <v>427</v>
+        <v>491</v>
       </c>
       <c r="M2" t="s">
-        <v>428</v>
+        <v>492</v>
       </c>
       <c r="N2" t="s">
-        <v>429</v>
+        <v>493</v>
       </c>
       <c r="O2" t="s">
-        <v>430</v>
+        <v>494</v>
       </c>
       <c r="P2" t="s">
-        <v>431</v>
+        <v>495</v>
       </c>
       <c r="Q2" t="s">
-        <v>432</v>
+        <v>496</v>
       </c>
       <c r="R2" t="s">
-        <v>433</v>
+        <v>497</v>
       </c>
       <c r="S2" t="s">
-        <v>434</v>
+        <v>498</v>
       </c>
       <c r="T2" t="s">
-        <v>435</v>
+        <v>499</v>
       </c>
       <c r="U2" t="s">
-        <v>436</v>
+        <v>500</v>
       </c>
       <c r="V2" t="s">
-        <v>437</v>
+        <v>501</v>
       </c>
       <c r="W2" t="s">
-        <v>438</v>
+        <v>502</v>
       </c>
       <c r="X2" t="s">
-        <v>439</v>
+        <v>503</v>
       </c>
       <c r="Y2" t="s">
-        <v>440</v>
+        <v>504</v>
       </c>
       <c r="Z2" t="s">
-        <v>440</v>
+        <v>504</v>
       </c>
       <c r="AA2" t="s">
-        <v>441</v>
+        <v>505</v>
       </c>
       <c r="AB2" t="s">
-        <v>442</v>
+        <v>506</v>
       </c>
     </row>
     <row r="3" spans="1:28">
@@ -1773,7 +2072,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C3">
         <v>1049</v>
@@ -1859,7 +2158,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C4">
         <v>1098</v>
@@ -1945,7 +2244,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>1143</v>
@@ -2031,7 +2330,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>994</v>
@@ -2117,7 +2416,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>1155</v>
@@ -2203,7 +2502,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C8">
         <v>1145</v>
@@ -2289,7 +2588,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <v>898</v>
@@ -2375,7 +2674,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="C10">
         <v>1036</v>
@@ -2461,7 +2760,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C11">
         <v>1137</v>
@@ -2547,7 +2846,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C12">
         <v>1012</v>
@@ -2633,7 +2932,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C13">
         <v>1108</v>
@@ -2719,7 +3018,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="C14">
         <v>862</v>
@@ -2805,7 +3104,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C15">
         <v>849</v>
@@ -2891,7 +3190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C16">
         <v>848</v>
@@ -2977,7 +3276,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="C17">
         <v>741</v>
@@ -3063,7 +3362,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="C18">
         <v>625</v>
@@ -3149,7 +3448,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="C19">
         <v>1067</v>
@@ -3235,7 +3534,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="C20">
         <v>1035</v>
@@ -3321,7 +3620,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="C21">
         <v>1062</v>
@@ -3407,7 +3706,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C22">
         <v>959</v>
@@ -3493,7 +3792,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C23">
         <v>998</v>
@@ -3579,7 +3878,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="C24">
         <v>1193</v>
@@ -3665,7 +3964,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C25">
         <v>967</v>
@@ -3751,7 +4050,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="C26">
         <v>834</v>
@@ -3837,7 +4136,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C27">
         <v>643</v>
@@ -3923,7 +4222,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C28">
         <v>652</v>
@@ -4009,7 +4308,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="C29">
         <v>1142</v>
@@ -4095,7 +4394,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C30">
         <v>1108</v>
@@ -4181,7 +4480,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="C31">
         <v>996</v>
@@ -4267,7 +4566,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C32">
         <v>1076</v>
@@ -4353,7 +4652,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C33">
         <v>1060</v>
@@ -4439,7 +4738,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C34">
         <v>1213</v>
@@ -4525,7 +4824,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="C35">
         <v>1063</v>
@@ -4611,7 +4910,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="C36">
         <v>903</v>
@@ -4697,7 +4996,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C37">
         <v>851</v>
@@ -4783,7 +5082,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="C38">
         <v>972</v>
@@ -4869,7 +5168,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C39">
         <v>853</v>
@@ -4955,7 +5254,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C40">
         <v>906</v>
@@ -5041,7 +5340,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="C41">
         <v>790</v>
@@ -5127,7 +5426,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="C42">
         <v>963</v>
@@ -5213,7 +5512,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="C43">
         <v>772</v>
@@ -5299,7 +5598,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="C44">
         <v>972</v>
@@ -5385,7 +5684,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C45">
         <v>990</v>
@@ -5471,7 +5770,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="C46">
         <v>1041</v>
@@ -5557,7 +5856,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="C47">
         <v>1133</v>
@@ -5643,7 +5942,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="C48">
         <v>840</v>
@@ -5729,7 +6028,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C49">
         <v>878</v>
@@ -5815,7 +6114,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="C50">
         <v>1026</v>
@@ -5901,7 +6200,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C51">
         <v>935</v>
@@ -5987,7 +6286,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="C52">
         <v>991</v>
@@ -6073,7 +6372,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="C53">
         <v>1047</v>
@@ -6159,7 +6458,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="C54">
         <v>999</v>
@@ -6245,7 +6544,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="C55">
         <v>1027</v>
@@ -6331,7 +6630,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="C56">
         <v>920</v>
@@ -6417,7 +6716,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="C57">
         <v>1127</v>
@@ -6503,7 +6802,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="C58">
         <v>806</v>
@@ -6589,7 +6888,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="C59">
         <v>648</v>
@@ -6675,7 +6974,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="C60">
         <v>634</v>
@@ -6761,7 +7060,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="C61">
         <v>671</v>
@@ -6847,7 +7146,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="C62">
         <v>825</v>
@@ -6933,7 +7232,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="C63">
         <v>955</v>
@@ -7019,7 +7318,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="C64">
         <v>1100</v>
@@ -7105,7 +7404,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C65">
         <v>790</v>
@@ -7191,7 +7490,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="C66">
         <v>1016</v>
@@ -7277,7 +7576,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="C67">
         <v>891</v>
@@ -7363,7 +7662,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="C68">
         <v>1182</v>
@@ -7449,7 +7748,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="C69">
         <v>987</v>
@@ -7535,7 +7834,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="C70">
         <v>1030</v>
@@ -7621,7 +7920,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="C71">
         <v>1009</v>
@@ -7707,7 +8006,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="C72">
         <v>998</v>
@@ -7793,7 +8092,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C73">
         <v>997</v>
@@ -7879,7 +8178,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="C74">
         <v>1047</v>
@@ -7965,7 +8264,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="C75">
         <v>1208</v>
@@ -8051,7 +8350,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="C76">
         <v>555</v>
@@ -8137,7 +8436,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="C77">
         <v>1157</v>
@@ -8223,7 +8522,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="C78">
         <v>1173</v>
@@ -8309,7 +8608,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="C79">
         <v>562</v>
@@ -8395,7 +8694,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="C80">
         <v>705</v>
@@ -8481,7 +8780,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="C81">
         <v>1057</v>
@@ -8567,7 +8866,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="C82">
         <v>983</v>
@@ -8653,7 +8952,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="C83">
         <v>1102</v>
@@ -8739,7 +9038,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="C84">
         <v>665</v>
@@ -8825,7 +9124,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="C85">
         <v>584</v>
@@ -8911,7 +9210,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="C86">
         <v>635</v>
@@ -8997,7 +9296,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="C87">
         <v>648</v>
@@ -9083,7 +9382,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="C88">
         <v>700</v>
@@ -9169,7 +9468,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="C89">
         <v>555</v>
@@ -9255,7 +9554,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="C90">
         <v>1058</v>
@@ -9341,7 +9640,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="C91">
         <v>740</v>
@@ -9427,7 +9726,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="C92">
         <v>667</v>
@@ -9513,7 +9812,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="C93">
         <v>1112</v>
@@ -9599,7 +9898,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="C94">
         <v>721</v>
@@ -9685,7 +9984,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="C95">
         <v>1096</v>
@@ -9771,7 +10070,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="C96">
         <v>1090</v>
@@ -9857,7 +10156,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="C97">
         <v>1093</v>
@@ -9943,7 +10242,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="C98">
         <v>1043</v>
@@ -10029,7 +10328,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="C99">
         <v>1151</v>
@@ -10115,7 +10414,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="C100">
         <v>641</v>
@@ -10201,7 +10500,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="C101">
         <v>728</v>
@@ -10287,7 +10586,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C102">
         <v>1183</v>
@@ -10373,7 +10672,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="C103">
         <v>639</v>
@@ -10459,7 +10758,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="C104">
         <v>792</v>
@@ -10545,7 +10844,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="C105">
         <v>1100</v>
@@ -10631,7 +10930,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="C106">
         <v>888</v>
@@ -10717,7 +11016,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="C107">
         <v>1095</v>
@@ -10803,7 +11102,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C108">
         <v>1037</v>
@@ -10889,7 +11188,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="C109">
         <v>844</v>
@@ -10975,7 +11274,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="C110">
         <v>841</v>
@@ -11061,7 +11360,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="C111">
         <v>952</v>
@@ -11147,7 +11446,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="C112">
         <v>487</v>
@@ -11233,7 +11532,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="C113">
         <v>671</v>
@@ -11319,7 +11618,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="C114">
         <v>988</v>
@@ -11405,7 +11704,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="C115">
         <v>907</v>
@@ -11491,7 +11790,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="C116">
         <v>652</v>
@@ -11577,7 +11876,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="C117">
         <v>772</v>
@@ -11663,7 +11962,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="C118">
         <v>741</v>
@@ -11749,7 +12048,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="C119">
         <v>537</v>
@@ -11835,7 +12134,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="C120">
         <v>882</v>
@@ -11921,7 +12220,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="C121">
         <v>721</v>
@@ -12007,7 +12306,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="C122">
         <v>634</v>
@@ -12093,7 +12392,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="C123">
         <v>1069</v>
@@ -12179,7 +12478,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="C124">
         <v>725</v>
@@ -12265,7 +12564,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="C125">
         <v>561</v>
@@ -12351,7 +12650,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="C126">
         <v>650</v>
@@ -12437,7 +12736,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="C127">
         <v>915</v>
@@ -12523,7 +12822,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="C128">
         <v>682</v>
@@ -12609,7 +12908,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="C129">
         <v>828</v>
@@ -12695,7 +12994,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="C130">
         <v>1017</v>
@@ -12781,7 +13080,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="C131">
         <v>1028</v>
@@ -12867,7 +13166,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="C132">
         <v>1033</v>
@@ -12953,7 +13252,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="C133">
         <v>750</v>
@@ -13039,7 +13338,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="C134">
         <v>698</v>
@@ -13125,7 +13424,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="C135">
         <v>591</v>
@@ -13211,7 +13510,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="C136">
         <v>1067</v>
@@ -13297,7 +13596,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="C137">
         <v>1138</v>
@@ -13383,7 +13682,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="C138">
         <v>1035</v>
@@ -13469,7 +13768,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="C139">
         <v>1054</v>
@@ -13555,7 +13854,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="C140">
         <v>894</v>
@@ -13641,7 +13940,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="C141">
         <v>1016</v>
@@ -13727,7 +14026,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="C142">
         <v>1090</v>
@@ -13813,7 +14112,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="C143">
         <v>965</v>
@@ -13899,7 +14198,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="C144">
         <v>1091</v>
@@ -13985,7 +14284,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="C145">
         <v>930</v>
@@ -14071,7 +14370,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="C146">
         <v>1032</v>
@@ -14157,7 +14456,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="C147">
         <v>1066</v>
@@ -14243,7 +14542,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="C148">
         <v>1118</v>
@@ -14329,7 +14628,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="C149">
         <v>1003</v>
@@ -14415,7 +14714,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="C150">
         <v>1009</v>
@@ -14501,7 +14800,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="C151">
         <v>1064</v>
@@ -14587,7 +14886,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="C152">
         <v>1163</v>
@@ -14673,7 +14972,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="C153">
         <v>1012</v>
@@ -14759,7 +15058,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="C154">
         <v>1006</v>
@@ -14845,7 +15144,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="C155">
         <v>638</v>
@@ -14931,7 +15230,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="C156">
         <v>713</v>
@@ -15017,7 +15316,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="C157">
         <v>1073</v>
@@ -15103,7 +15402,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="C158">
         <v>657</v>
@@ -15189,7 +15488,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="C159">
         <v>661</v>
@@ -15275,7 +15574,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="C160">
         <v>954</v>
@@ -15361,7 +15660,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="C161">
         <v>819</v>
@@ -15447,7 +15746,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>157</v>
+        <v>186</v>
       </c>
       <c r="C162">
         <v>700</v>
@@ -15533,7 +15832,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="C163">
         <v>1026</v>
@@ -15619,7 +15918,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="C164">
         <v>1127</v>
@@ -15705,7 +16004,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="C165">
         <v>1100</v>
@@ -15791,7 +16090,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="C166">
         <v>1019</v>
@@ -15877,7 +16176,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="C167">
         <v>1115</v>
@@ -15963,7 +16262,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="C168">
         <v>1126</v>
@@ -16049,7 +16348,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="C169">
         <v>1059</v>
@@ -16135,7 +16434,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="C170">
         <v>912</v>
@@ -16221,7 +16520,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="C171">
         <v>963</v>
@@ -16307,7 +16606,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="C172">
         <v>917</v>
@@ -16393,7 +16692,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="C173">
         <v>886</v>
@@ -16479,7 +16778,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="C174">
         <v>896</v>
@@ -16565,7 +16864,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="C175">
         <v>1088</v>
@@ -16651,7 +16950,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="C176">
         <v>769</v>
@@ -16737,7 +17036,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="C177">
         <v>984</v>
@@ -16823,7 +17122,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="C178">
         <v>1082</v>
@@ -16909,7 +17208,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="C179">
         <v>1110</v>
@@ -16995,7 +17294,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="C180">
         <v>1128</v>
@@ -17081,7 +17380,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="C181">
         <v>670</v>
@@ -17167,7 +17466,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="C182">
         <v>689</v>
@@ -17253,7 +17552,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="C183">
         <v>896</v>
@@ -17339,7 +17638,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="C184">
         <v>838</v>
@@ -17425,7 +17724,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="C185">
         <v>895</v>
@@ -17511,7 +17810,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="C186">
         <v>637</v>
@@ -17597,7 +17896,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="C187">
         <v>994</v>
@@ -17683,7 +17982,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="C188">
         <v>851</v>
@@ -17769,7 +18068,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="C189">
         <v>725</v>
@@ -17855,7 +18154,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="C190">
         <v>987</v>
@@ -17941,7 +18240,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="C191">
         <v>1010</v>
@@ -18027,7 +18326,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="C192">
         <v>990</v>
@@ -18113,7 +18412,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="C193">
         <v>885</v>
@@ -18199,7 +18498,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="C194">
         <v>406</v>
@@ -18285,7 +18584,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="C195">
         <v>1055</v>
@@ -18371,7 +18670,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="C196">
         <v>1100</v>
@@ -18457,7 +18756,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="C197">
         <v>1140</v>
@@ -18543,7 +18842,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c r="C198">
         <v>1111</v>
@@ -18629,7 +18928,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="C199">
         <v>1023</v>
@@ -18715,7 +19014,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="C200">
         <v>1127</v>
@@ -18801,7 +19100,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>196</v>
+        <v>224</v>
       </c>
       <c r="C201">
         <v>1013</v>
@@ -18887,7 +19186,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="C202">
         <v>645</v>
@@ -18973,7 +19272,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="C203">
         <v>861</v>
@@ -19059,7 +19358,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>199</v>
+        <v>227</v>
       </c>
       <c r="C204">
         <v>550</v>
@@ -19145,7 +19444,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="C205">
         <v>992</v>
@@ -19231,7 +19530,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>201</v>
+        <v>229</v>
       </c>
       <c r="C206">
         <v>847</v>
@@ -19317,7 +19616,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="C207">
         <v>1136</v>
@@ -19403,7 +19702,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="C208">
         <v>952</v>
@@ -19489,7 +19788,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="C209">
         <v>795</v>
@@ -19575,7 +19874,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="C210">
         <v>1031</v>
@@ -19661,7 +19960,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="C211">
         <v>839</v>
@@ -19747,7 +20046,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="C212">
         <v>1076</v>
@@ -19833,7 +20132,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>208</v>
+        <v>235</v>
       </c>
       <c r="C213">
         <v>1092</v>
@@ -19919,7 +20218,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="C214">
         <v>1043</v>
@@ -20005,7 +20304,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="C215">
         <v>863</v>
@@ -20091,7 +20390,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="C216">
         <v>876</v>
@@ -20177,7 +20476,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="C217">
         <v>1187</v>
@@ -20263,7 +20562,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C218">
         <v>1168</v>
@@ -20349,7 +20648,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>214</v>
+        <v>241</v>
       </c>
       <c r="C219">
         <v>1077</v>
@@ -20435,7 +20734,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="C220">
         <v>942</v>
@@ -20521,7 +20820,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="C221">
         <v>1120</v>
@@ -20607,7 +20906,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="C222">
         <v>649</v>
@@ -20693,7 +20992,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="C223">
         <v>715</v>
@@ -20779,7 +21078,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="C224">
         <v>758</v>
@@ -20865,7 +21164,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="C225">
         <v>746</v>
@@ -20951,7 +21250,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="C226">
         <v>807</v>
@@ -21037,7 +21336,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>201</v>
+        <v>249</v>
       </c>
       <c r="C227">
         <v>859</v>
@@ -21123,7 +21422,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="C228">
         <v>745</v>
@@ -21209,7 +21508,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="C229">
         <v>648</v>
@@ -21295,7 +21594,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="C230">
         <v>578</v>
@@ -21381,7 +21680,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="C231">
         <v>1097</v>
@@ -21467,7 +21766,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="C232">
         <v>1043</v>
@@ -21553,7 +21852,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>227</v>
+        <v>255</v>
       </c>
       <c r="C233">
         <v>954</v>
@@ -21639,7 +21938,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="C234">
         <v>1081</v>
@@ -21725,7 +22024,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="C235">
         <v>621</v>
@@ -21811,7 +22110,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="C236">
         <v>1016</v>
@@ -21897,7 +22196,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="C237">
         <v>635</v>
@@ -21983,7 +22282,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="C238">
         <v>864</v>
@@ -22069,7 +22368,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="C239">
         <v>942</v>
@@ -22155,7 +22454,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>234</v>
+        <v>262</v>
       </c>
       <c r="C240">
         <v>971</v>
@@ -22241,7 +22540,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="C241">
         <v>639</v>
@@ -22327,7 +22626,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>236</v>
+        <v>264</v>
       </c>
       <c r="C242">
         <v>790</v>
@@ -22413,7 +22712,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="C243">
         <v>985</v>
@@ -22499,7 +22798,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="C244">
         <v>667</v>
@@ -22585,7 +22884,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>239</v>
+        <v>267</v>
       </c>
       <c r="C245">
         <v>357</v>
@@ -22671,7 +22970,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="C246">
         <v>600</v>
@@ -22757,7 +23056,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>241</v>
+        <v>269</v>
       </c>
       <c r="C247">
         <v>618</v>
@@ -22843,7 +23142,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="C248">
         <v>728</v>
@@ -22929,7 +23228,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="C249">
         <v>484</v>
@@ -23015,7 +23314,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>244</v>
+        <v>272</v>
       </c>
       <c r="C250">
         <v>994</v>
@@ -23101,7 +23400,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>245</v>
+        <v>273</v>
       </c>
       <c r="C251">
         <v>572</v>
@@ -23187,7 +23486,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>246</v>
+        <v>274</v>
       </c>
       <c r="C252">
         <v>652</v>
@@ -23273,7 +23572,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="C253">
         <v>705</v>
@@ -23359,7 +23658,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>218</v>
+        <v>276</v>
       </c>
       <c r="C254">
         <v>752</v>
@@ -23445,7 +23744,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="C255">
         <v>823</v>
@@ -23531,7 +23830,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="C256">
         <v>902</v>
@@ -23617,7 +23916,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>220</v>
+        <v>279</v>
       </c>
       <c r="C257">
         <v>749</v>
@@ -23703,7 +24002,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>249</v>
+        <v>280</v>
       </c>
       <c r="C258">
         <v>828</v>
@@ -23789,7 +24088,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>217</v>
+        <v>281</v>
       </c>
       <c r="C259">
         <v>1008</v>
@@ -23875,7 +24174,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>218</v>
+        <v>282</v>
       </c>
       <c r="C260">
         <v>1039</v>
@@ -23961,7 +24260,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="C261">
         <v>823</v>
@@ -24047,7 +24346,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
       <c r="C262">
         <v>971</v>
@@ -24133,7 +24432,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>252</v>
+        <v>284</v>
       </c>
       <c r="C263">
         <v>919</v>
@@ -24219,7 +24518,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>201</v>
+        <v>285</v>
       </c>
       <c r="C264">
         <v>913</v>
@@ -24305,7 +24604,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>222</v>
+        <v>286</v>
       </c>
       <c r="C265">
         <v>885</v>
@@ -24391,7 +24690,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>253</v>
+        <v>287</v>
       </c>
       <c r="C266">
         <v>595</v>
@@ -24477,7 +24776,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>254</v>
+        <v>288</v>
       </c>
       <c r="C267">
         <v>945</v>
@@ -24563,7 +24862,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>255</v>
+        <v>289</v>
       </c>
       <c r="C268">
         <v>1099</v>
@@ -24649,7 +24948,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>256</v>
+        <v>290</v>
       </c>
       <c r="C269">
         <v>620</v>
@@ -24735,7 +25034,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>257</v>
+        <v>291</v>
       </c>
       <c r="C270">
         <v>630</v>
@@ -24821,7 +25120,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>258</v>
+        <v>292</v>
       </c>
       <c r="C271">
         <v>1137</v>
@@ -24907,7 +25206,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>259</v>
+        <v>293</v>
       </c>
       <c r="C272">
         <v>669</v>
@@ -24993,7 +25292,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>260</v>
+        <v>289</v>
       </c>
       <c r="C273">
         <v>920</v>
@@ -25079,7 +25378,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="C274">
         <v>873</v>
@@ -25165,7 +25464,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>262</v>
+        <v>295</v>
       </c>
       <c r="C275">
         <v>617</v>
@@ -25251,7 +25550,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="C276">
         <v>604</v>
@@ -25337,7 +25636,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="C277">
         <v>796</v>
@@ -25423,7 +25722,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>265</v>
+        <v>298</v>
       </c>
       <c r="C278">
         <v>1152</v>
@@ -25509,7 +25808,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>266</v>
+        <v>299</v>
       </c>
       <c r="C279">
         <v>959</v>
@@ -25595,7 +25894,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>267</v>
+        <v>300</v>
       </c>
       <c r="C280">
         <v>1001</v>
@@ -25681,7 +25980,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>268</v>
+        <v>301</v>
       </c>
       <c r="C281">
         <v>1139</v>
@@ -25767,7 +26066,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c r="C282">
         <v>1185</v>
@@ -25853,7 +26152,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>270</v>
+        <v>303</v>
       </c>
       <c r="C283">
         <v>1077</v>
@@ -25939,7 +26238,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="C284">
         <v>1142</v>
@@ -26025,7 +26324,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="C285">
         <v>1077</v>
@@ -26111,7 +26410,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>273</v>
+        <v>306</v>
       </c>
       <c r="C286">
         <v>1088</v>
@@ -26197,7 +26496,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>200</v>
+        <v>307</v>
       </c>
       <c r="C287">
         <v>913</v>
@@ -26283,7 +26582,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="C288">
         <v>899</v>
@@ -26369,7 +26668,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>275</v>
+        <v>309</v>
       </c>
       <c r="C289">
         <v>664</v>
@@ -26455,7 +26754,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>276</v>
+        <v>310</v>
       </c>
       <c r="C290">
         <v>698</v>
@@ -26541,7 +26840,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="C291">
         <v>833</v>
@@ -26627,7 +26926,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
       <c r="C292">
         <v>501</v>
@@ -26713,7 +27012,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>279</v>
+        <v>313</v>
       </c>
       <c r="C293">
         <v>631</v>
@@ -26799,7 +27098,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>280</v>
+        <v>314</v>
       </c>
       <c r="C294">
         <v>603</v>
@@ -26885,7 +27184,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>281</v>
+        <v>315</v>
       </c>
       <c r="C295">
         <v>657</v>
@@ -26971,7 +27270,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="C296">
         <v>680</v>
@@ -27057,7 +27356,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="C297">
         <v>668</v>
@@ -27143,7 +27442,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>284</v>
+        <v>318</v>
       </c>
       <c r="C298">
         <v>804</v>
@@ -27229,7 +27528,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>285</v>
+        <v>319</v>
       </c>
       <c r="C299">
         <v>933</v>
@@ -27315,7 +27614,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>286</v>
+        <v>320</v>
       </c>
       <c r="C300">
         <v>806</v>
@@ -27401,7 +27700,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>287</v>
+        <v>321</v>
       </c>
       <c r="C301">
         <v>733</v>
@@ -27487,7 +27786,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>288</v>
+        <v>322</v>
       </c>
       <c r="C302">
         <v>1153</v>
@@ -27573,7 +27872,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>289</v>
+        <v>323</v>
       </c>
       <c r="C303">
         <v>646</v>
@@ -27659,7 +27958,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>290</v>
+        <v>324</v>
       </c>
       <c r="C304">
         <v>986</v>
@@ -27745,7 +28044,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>291</v>
+        <v>325</v>
       </c>
       <c r="C305">
         <v>1013</v>
@@ -27831,7 +28130,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>201</v>
+        <v>326</v>
       </c>
       <c r="C306">
         <v>1060</v>
@@ -27917,7 +28216,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>222</v>
+        <v>327</v>
       </c>
       <c r="C307">
         <v>1097</v>
@@ -28003,7 +28302,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="C308">
         <v>772</v>
@@ -28089,7 +28388,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>293</v>
+        <v>324</v>
       </c>
       <c r="C309">
         <v>1172</v>
@@ -28175,7 +28474,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>294</v>
+        <v>329</v>
       </c>
       <c r="C310">
         <v>658</v>
@@ -28261,7 +28560,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>295</v>
+        <v>330</v>
       </c>
       <c r="C311">
         <v>963</v>
@@ -28347,7 +28646,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>296</v>
+        <v>331</v>
       </c>
       <c r="C312">
         <v>1202</v>
@@ -28433,7 +28732,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>297</v>
+        <v>332</v>
       </c>
       <c r="C313">
         <v>604</v>
@@ -28519,7 +28818,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>298</v>
+        <v>333</v>
       </c>
       <c r="C314">
         <v>1218</v>
@@ -28605,7 +28904,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>201</v>
+        <v>334</v>
       </c>
       <c r="C315">
         <v>798</v>
@@ -28691,7 +28990,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>222</v>
+        <v>335</v>
       </c>
       <c r="C316">
         <v>838</v>
@@ -28777,7 +29076,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>292</v>
+        <v>336</v>
       </c>
       <c r="C317">
         <v>918</v>
@@ -28863,7 +29162,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>293</v>
+        <v>337</v>
       </c>
       <c r="C318">
         <v>822</v>
@@ -28949,7 +29248,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>294</v>
+        <v>338</v>
       </c>
       <c r="C319">
         <v>661</v>
@@ -29035,7 +29334,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="C320">
         <v>1157</v>
@@ -29121,7 +29420,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>82</v>
+        <v>340</v>
       </c>
       <c r="C321">
         <v>873</v>
@@ -29207,7 +29506,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>83</v>
+        <v>341</v>
       </c>
       <c r="C322">
         <v>1044</v>
@@ -29293,7 +29592,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>299</v>
+        <v>342</v>
       </c>
       <c r="C323">
         <v>1187</v>
@@ -29379,7 +29678,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>300</v>
+        <v>343</v>
       </c>
       <c r="C324">
         <v>999</v>
@@ -29465,7 +29764,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>301</v>
+        <v>344</v>
       </c>
       <c r="C325">
         <v>1010</v>
@@ -29551,7 +29850,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>302</v>
+        <v>345</v>
       </c>
       <c r="C326">
         <v>981</v>
@@ -29637,7 +29936,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>303</v>
+        <v>346</v>
       </c>
       <c r="C327">
         <v>780</v>
@@ -29723,7 +30022,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>304</v>
+        <v>347</v>
       </c>
       <c r="C328">
         <v>1058</v>
@@ -29809,7 +30108,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>305</v>
+        <v>348</v>
       </c>
       <c r="C329">
         <v>1029</v>
@@ -29895,7 +30194,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>306</v>
+        <v>349</v>
       </c>
       <c r="C330">
         <v>1011</v>
@@ -29981,7 +30280,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>307</v>
+        <v>350</v>
       </c>
       <c r="C331">
         <v>1000</v>
@@ -30067,7 +30366,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>308</v>
+        <v>351</v>
       </c>
       <c r="C332">
         <v>1128</v>
@@ -30153,7 +30452,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="C333">
         <v>1190</v>
@@ -30239,7 +30538,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>310</v>
+        <v>353</v>
       </c>
       <c r="C334">
         <v>1203</v>
@@ -30325,7 +30624,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>311</v>
+        <v>354</v>
       </c>
       <c r="C335">
         <v>1197</v>
@@ -30411,7 +30710,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>312</v>
+        <v>355</v>
       </c>
       <c r="C336">
         <v>1225</v>
@@ -30497,7 +30796,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>313</v>
+        <v>356</v>
       </c>
       <c r="C337">
         <v>743</v>
@@ -30583,7 +30882,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>314</v>
+        <v>357</v>
       </c>
       <c r="C338">
         <v>1055</v>
@@ -30669,7 +30968,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>315</v>
+        <v>358</v>
       </c>
       <c r="C339">
         <v>1058</v>
@@ -30755,7 +31054,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>316</v>
+        <v>359</v>
       </c>
       <c r="C340">
         <v>634</v>
@@ -30841,7 +31140,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>317</v>
+        <v>360</v>
       </c>
       <c r="C341">
         <v>595</v>
@@ -30927,7 +31226,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>318</v>
+        <v>361</v>
       </c>
       <c r="C342">
         <v>1208</v>
@@ -31013,7 +31312,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>319</v>
+        <v>362</v>
       </c>
       <c r="C343">
         <v>759</v>
@@ -31099,7 +31398,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>320</v>
+        <v>363</v>
       </c>
       <c r="C344">
         <v>839</v>
@@ -31185,7 +31484,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>240</v>
+        <v>364</v>
       </c>
       <c r="C345">
         <v>1186</v>
@@ -31271,7 +31570,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>231</v>
+        <v>365</v>
       </c>
       <c r="C346">
         <v>1040</v>
@@ -31357,7 +31656,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>232</v>
+        <v>366</v>
       </c>
       <c r="C347">
         <v>1091</v>
@@ -31443,7 +31742,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>321</v>
+        <v>367</v>
       </c>
       <c r="C348">
         <v>747</v>
@@ -31529,7 +31828,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>322</v>
+        <v>368</v>
       </c>
       <c r="C349">
         <v>720</v>
@@ -31615,7 +31914,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>323</v>
+        <v>369</v>
       </c>
       <c r="C350">
         <v>942</v>
@@ -31701,7 +32000,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>324</v>
+        <v>370</v>
       </c>
       <c r="C351">
         <v>995</v>
@@ -31787,7 +32086,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>325</v>
+        <v>371</v>
       </c>
       <c r="C352">
         <v>633</v>
@@ -31873,7 +32172,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>326</v>
+        <v>372</v>
       </c>
       <c r="C353">
         <v>741</v>
@@ -31959,7 +32258,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>327</v>
+        <v>373</v>
       </c>
       <c r="C354">
         <v>1047</v>
@@ -32045,7 +32344,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>328</v>
+        <v>374</v>
       </c>
       <c r="C355">
         <v>1150</v>
@@ -32131,7 +32430,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="C356">
         <v>1032</v>
@@ -32217,7 +32516,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>330</v>
+        <v>376</v>
       </c>
       <c r="C357">
         <v>1075</v>
@@ -32303,7 +32602,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>331</v>
+        <v>377</v>
       </c>
       <c r="C358">
         <v>1075</v>
@@ -32389,7 +32688,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>332</v>
+        <v>378</v>
       </c>
       <c r="C359">
         <v>1130</v>
@@ -32475,7 +32774,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>333</v>
+        <v>379</v>
       </c>
       <c r="C360">
         <v>1133</v>
@@ -32561,7 +32860,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>334</v>
+        <v>380</v>
       </c>
       <c r="C361">
         <v>881</v>
@@ -32647,7 +32946,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>335</v>
+        <v>381</v>
       </c>
       <c r="C362">
         <v>852</v>
@@ -32733,7 +33032,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C363">
         <v>1123</v>
@@ -32819,7 +33118,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>337</v>
+        <v>383</v>
       </c>
       <c r="C364">
         <v>1126</v>
@@ -32905,7 +33204,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>338</v>
+        <v>384</v>
       </c>
       <c r="C365">
         <v>1038</v>
@@ -32991,7 +33290,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>339</v>
+        <v>385</v>
       </c>
       <c r="C366">
         <v>920</v>
@@ -33077,7 +33376,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>340</v>
+        <v>386</v>
       </c>
       <c r="C367">
         <v>777</v>
@@ -33163,7 +33462,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>341</v>
+        <v>387</v>
       </c>
       <c r="C368">
         <v>1002</v>
@@ -33249,7 +33548,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>342</v>
+        <v>388</v>
       </c>
       <c r="C369">
         <v>1123</v>
@@ -33335,7 +33634,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>343</v>
+        <v>389</v>
       </c>
       <c r="C370">
         <v>737</v>
@@ -33421,7 +33720,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>344</v>
+        <v>390</v>
       </c>
       <c r="C371">
         <v>923</v>
@@ -33507,7 +33806,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>345</v>
+        <v>391</v>
       </c>
       <c r="C372">
         <v>623</v>
@@ -33593,7 +33892,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>346</v>
+        <v>392</v>
       </c>
       <c r="C373">
         <v>885</v>
@@ -33679,7 +33978,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>275</v>
+        <v>393</v>
       </c>
       <c r="C374">
         <v>716</v>
@@ -33765,7 +34064,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>276</v>
+        <v>394</v>
       </c>
       <c r="C375">
         <v>757</v>
@@ -33851,7 +34150,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>347</v>
+        <v>395</v>
       </c>
       <c r="C376">
         <v>951</v>
@@ -33937,7 +34236,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>348</v>
+        <v>396</v>
       </c>
       <c r="C377">
         <v>1079</v>
@@ -34023,7 +34322,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="C378">
         <v>307</v>
@@ -34109,7 +34408,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>350</v>
+        <v>398</v>
       </c>
       <c r="C379">
         <v>905</v>
@@ -34195,7 +34494,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>351</v>
+        <v>399</v>
       </c>
       <c r="C380">
         <v>910</v>
@@ -34281,7 +34580,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>352</v>
+        <v>400</v>
       </c>
       <c r="C381">
         <v>741</v>
@@ -34367,7 +34666,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>350</v>
+        <v>401</v>
       </c>
       <c r="C382">
         <v>1103</v>
@@ -34453,7 +34752,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>353</v>
+        <v>402</v>
       </c>
       <c r="C383">
         <v>659</v>
@@ -34539,7 +34838,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>354</v>
+        <v>403</v>
       </c>
       <c r="C384">
         <v>680</v>
@@ -34625,7 +34924,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>355</v>
+        <v>404</v>
       </c>
       <c r="C385">
         <v>1060</v>
@@ -34711,7 +35010,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>356</v>
+        <v>405</v>
       </c>
       <c r="C386">
         <v>1056</v>
@@ -34797,7 +35096,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>357</v>
+        <v>406</v>
       </c>
       <c r="C387">
         <v>1004</v>
@@ -34883,7 +35182,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>358</v>
+        <v>407</v>
       </c>
       <c r="C388">
         <v>1013</v>
@@ -34969,7 +35268,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>359</v>
+        <v>408</v>
       </c>
       <c r="C389">
         <v>1156</v>
@@ -35055,7 +35354,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>360</v>
+        <v>409</v>
       </c>
       <c r="C390">
         <v>990</v>
@@ -35141,7 +35440,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>361</v>
+        <v>410</v>
       </c>
       <c r="C391">
         <v>771</v>
@@ -35227,7 +35526,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>362</v>
+        <v>411</v>
       </c>
       <c r="C392">
         <v>814</v>
@@ -35313,7 +35612,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>247</v>
+        <v>412</v>
       </c>
       <c r="C393">
         <v>977</v>
@@ -35399,7 +35698,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>247</v>
+        <v>413</v>
       </c>
       <c r="C394">
         <v>661</v>
@@ -35485,7 +35784,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>363</v>
+        <v>414</v>
       </c>
       <c r="C395">
         <v>587</v>
@@ -35571,7 +35870,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>364</v>
+        <v>415</v>
       </c>
       <c r="C396">
         <v>1154</v>
@@ -35657,7 +35956,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>365</v>
+        <v>416</v>
       </c>
       <c r="C397">
         <v>1122</v>
@@ -35743,7 +36042,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>366</v>
+        <v>417</v>
       </c>
       <c r="C398">
         <v>1102</v>
@@ -35829,7 +36128,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>367</v>
+        <v>418</v>
       </c>
       <c r="C399">
         <v>1120</v>
@@ -35915,7 +36214,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>368</v>
+        <v>419</v>
       </c>
       <c r="C400">
         <v>1052</v>
@@ -36001,7 +36300,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>369</v>
+        <v>420</v>
       </c>
       <c r="C401">
         <v>1083</v>
@@ -36087,7 +36386,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>370</v>
+        <v>421</v>
       </c>
       <c r="C402">
         <v>1052</v>
@@ -36173,7 +36472,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>371</v>
+        <v>422</v>
       </c>
       <c r="C403">
         <v>1121</v>
@@ -36259,7 +36558,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>372</v>
+        <v>423</v>
       </c>
       <c r="C404">
         <v>1004</v>
@@ -36345,7 +36644,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>373</v>
+        <v>424</v>
       </c>
       <c r="C405">
         <v>999</v>
@@ -36431,7 +36730,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>374</v>
+        <v>425</v>
       </c>
       <c r="C406">
         <v>948</v>
@@ -36517,7 +36816,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>375</v>
+        <v>426</v>
       </c>
       <c r="C407">
         <v>1114</v>
@@ -36603,7 +36902,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>376</v>
+        <v>427</v>
       </c>
       <c r="C408">
         <v>624</v>
@@ -36689,7 +36988,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>377</v>
+        <v>428</v>
       </c>
       <c r="C409">
         <v>604</v>
@@ -36775,7 +37074,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>378</v>
+        <v>429</v>
       </c>
       <c r="C410">
         <v>1115</v>
@@ -36861,7 +37160,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>379</v>
+        <v>430</v>
       </c>
       <c r="C411">
         <v>1040</v>
@@ -36947,7 +37246,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>380</v>
+        <v>431</v>
       </c>
       <c r="C412">
         <v>1111</v>
@@ -37033,7 +37332,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>381</v>
+        <v>432</v>
       </c>
       <c r="C413">
         <v>1133</v>
@@ -37119,7 +37418,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>382</v>
+        <v>433</v>
       </c>
       <c r="C414">
         <v>1183</v>
@@ -37205,7 +37504,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>383</v>
+        <v>434</v>
       </c>
       <c r="C415">
         <v>979</v>
@@ -37291,7 +37590,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>384</v>
+        <v>435</v>
       </c>
       <c r="C416">
         <v>1006</v>
@@ -37377,7 +37676,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>385</v>
+        <v>436</v>
       </c>
       <c r="C417">
         <v>738</v>
@@ -37463,7 +37762,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>386</v>
+        <v>437</v>
       </c>
       <c r="C418">
         <v>909</v>
@@ -37549,7 +37848,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>387</v>
+        <v>438</v>
       </c>
       <c r="C419">
         <v>1103</v>
@@ -37635,7 +37934,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>388</v>
+        <v>439</v>
       </c>
       <c r="C420">
         <v>1014</v>
@@ -37721,7 +38020,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>245</v>
+        <v>440</v>
       </c>
       <c r="C421">
         <v>792</v>
@@ -37807,7 +38106,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>246</v>
+        <v>441</v>
       </c>
       <c r="C422">
         <v>793</v>
@@ -37893,7 +38192,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>389</v>
+        <v>442</v>
       </c>
       <c r="C423">
         <v>674</v>
@@ -37979,7 +38278,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
       <c r="C424">
         <v>766</v>
@@ -38065,7 +38364,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>391</v>
+        <v>444</v>
       </c>
       <c r="C425">
         <v>993</v>
@@ -38151,7 +38450,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>392</v>
+        <v>445</v>
       </c>
       <c r="C426">
         <v>895</v>
@@ -38237,7 +38536,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>393</v>
+        <v>446</v>
       </c>
       <c r="C427">
         <v>702</v>
@@ -38323,7 +38622,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>394</v>
+        <v>447</v>
       </c>
       <c r="C428">
         <v>1177</v>
@@ -38409,7 +38708,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>231</v>
+        <v>448</v>
       </c>
       <c r="C429">
         <v>1034</v>
@@ -38495,7 +38794,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>232</v>
+        <v>449</v>
       </c>
       <c r="C430">
         <v>927</v>
@@ -38581,7 +38880,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>395</v>
+        <v>450</v>
       </c>
       <c r="C431">
         <v>650</v>
@@ -38667,7 +38966,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>396</v>
+        <v>451</v>
       </c>
       <c r="C432">
         <v>627</v>
@@ -38753,7 +39052,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>397</v>
+        <v>452</v>
       </c>
       <c r="C433">
         <v>782</v>
@@ -38839,7 +39138,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>398</v>
+        <v>453</v>
       </c>
       <c r="C434">
         <v>814</v>
@@ -38925,7 +39224,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>201</v>
+        <v>454</v>
       </c>
       <c r="C435">
         <v>1114</v>
@@ -39011,7 +39310,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>222</v>
+        <v>455</v>
       </c>
       <c r="C436">
         <v>1036</v>
@@ -39097,7 +39396,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>399</v>
+        <v>456</v>
       </c>
       <c r="C437">
         <v>1149</v>
@@ -39183,7 +39482,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>400</v>
+        <v>457</v>
       </c>
       <c r="C438">
         <v>1100</v>
@@ -39269,7 +39568,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>215</v>
+        <v>458</v>
       </c>
       <c r="C439">
         <v>1138</v>
@@ -39355,7 +39654,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>401</v>
+        <v>459</v>
       </c>
       <c r="C440">
         <v>817</v>
@@ -39441,7 +39740,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>402</v>
+        <v>460</v>
       </c>
       <c r="C441">
         <v>939</v>
@@ -39527,7 +39826,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>403</v>
+        <v>461</v>
       </c>
       <c r="C442">
         <v>832</v>
@@ -39613,7 +39912,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>231</v>
+        <v>462</v>
       </c>
       <c r="C443">
         <v>1173</v>
@@ -39699,7 +39998,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>232</v>
+        <v>463</v>
       </c>
       <c r="C444">
         <v>931</v>
@@ -39785,7 +40084,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>404</v>
+        <v>464</v>
       </c>
       <c r="C445">
         <v>665</v>
@@ -39871,7 +40170,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>405</v>
+        <v>465</v>
       </c>
       <c r="C446">
         <v>673</v>
@@ -39957,7 +40256,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>406</v>
+        <v>466</v>
       </c>
       <c r="C447">
         <v>624</v>
@@ -40043,7 +40342,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>407</v>
+        <v>467</v>
       </c>
       <c r="C448">
         <v>671</v>
@@ -40129,7 +40428,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>408</v>
+        <v>468</v>
       </c>
       <c r="C449">
         <v>1188</v>
@@ -40215,7 +40514,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>409</v>
+        <v>469</v>
       </c>
       <c r="C450">
         <v>1069</v>
@@ -40301,7 +40600,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>410</v>
+        <v>470</v>
       </c>
       <c r="C451">
         <v>884</v>
@@ -40387,7 +40686,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>411</v>
+        <v>471</v>
       </c>
       <c r="C452">
         <v>902</v>
@@ -40473,7 +40772,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>412</v>
+        <v>472</v>
       </c>
       <c r="C453">
         <v>683</v>
@@ -40559,7 +40858,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="s">
-        <v>413</v>
+        <v>473</v>
       </c>
       <c r="C454">
         <v>775</v>
@@ -40645,7 +40944,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="s">
-        <v>353</v>
+        <v>474</v>
       </c>
       <c r="C455">
         <v>1067</v>
@@ -40731,7 +41030,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="s">
-        <v>414</v>
+        <v>475</v>
       </c>
       <c r="C456">
         <v>973</v>
@@ -40817,7 +41116,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="s">
-        <v>415</v>
+        <v>476</v>
       </c>
       <c r="C457">
         <v>927</v>
@@ -40903,7 +41202,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="s">
-        <v>231</v>
+        <v>477</v>
       </c>
       <c r="C458">
         <v>622</v>
@@ -40989,7 +41288,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="s">
-        <v>232</v>
+        <v>478</v>
       </c>
       <c r="C459">
         <v>654</v>
@@ -41075,7 +41374,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="s">
-        <v>416</v>
+        <v>479</v>
       </c>
       <c r="C460">
         <v>986</v>
@@ -41161,7 +41460,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="s">
-        <v>417</v>
+        <v>480</v>
       </c>
       <c r="C461">
         <v>960</v>
@@ -41247,7 +41546,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="s">
-        <v>81</v>
+        <v>481</v>
       </c>
       <c r="C462">
         <v>381</v>
